--- a/BWI/bestwine_output/bestwine_Poland.xlsx
+++ b/BWI/bestwine_output/bestwine_Poland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA743"/>
+  <dimension ref="A1:AA747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -78274,6 +78274,458 @@
         </is>
       </c>
     </row>
+    <row r="744">
+      <c r="A744" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="B744" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="C744" s="2" t="inlineStr">
+        <is>
+          <t>78034</t>
+        </is>
+      </c>
+      <c r="D744" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E744" s="2" t="inlineStr">
+        <is>
+          <t>Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="F744" s="2" t="inlineStr">
+        <is>
+          <t>Województwo kujawsko-pomorskie, Powiat Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="G744" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Mokra 30</t>
+        </is>
+      </c>
+      <c r="H744" s="2" t="inlineStr">
+        <is>
+          <t>85-834</t>
+        </is>
+      </c>
+      <c r="I744" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.pl</t>
+        </is>
+      </c>
+      <c r="J744" s="2" t="inlineStr"/>
+      <c r="K744" s="2" t="inlineStr"/>
+      <c r="L744" s="2" t="inlineStr"/>
+      <c r="M744" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N744" s="2" t="inlineStr">
+        <is>
+          <t>lmucha@bidfood.pl</t>
+        </is>
+      </c>
+      <c r="O744" s="2" t="inlineStr">
+        <is>
+          <t>+48 52 360 75 01</t>
+        </is>
+      </c>
+      <c r="P744" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q744" s="2" t="inlineStr">
+        <is>
+          <t>5921987110</t>
+        </is>
+      </c>
+      <c r="R744" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/farutex/</t>
+        </is>
+      </c>
+      <c r="S744" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="T744" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="U744" s="2" t="inlineStr"/>
+      <c r="V744" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCg0GPcESE_uDY_WZJITDpUw</t>
+        </is>
+      </c>
+      <c r="W744" s="2" t="inlineStr">
+        <is>
+          <t>Łukasz Mucha</t>
+        </is>
+      </c>
+      <c r="X744" s="2" t="inlineStr">
+        <is>
+          <t>Manager of Purchasing Department</t>
+        </is>
+      </c>
+      <c r="Y744" s="2" t="inlineStr"/>
+      <c r="Z744" s="2" t="inlineStr"/>
+      <c r="AA744" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/%C5%82ukasz-mucha-972a6596</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="B745" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="C745" s="2" t="inlineStr">
+        <is>
+          <t>78034</t>
+        </is>
+      </c>
+      <c r="D745" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E745" s="2" t="inlineStr">
+        <is>
+          <t>Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="F745" s="2" t="inlineStr">
+        <is>
+          <t>Województwo kujawsko-pomorskie, Powiat Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="G745" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Mokra 30</t>
+        </is>
+      </c>
+      <c r="H745" s="2" t="inlineStr">
+        <is>
+          <t>85-834</t>
+        </is>
+      </c>
+      <c r="I745" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.pl</t>
+        </is>
+      </c>
+      <c r="J745" s="2" t="inlineStr"/>
+      <c r="K745" s="2" t="inlineStr"/>
+      <c r="L745" s="2" t="inlineStr"/>
+      <c r="M745" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N745" s="2" t="inlineStr">
+        <is>
+          <t>lmucha@bidfood.pl</t>
+        </is>
+      </c>
+      <c r="O745" s="2" t="inlineStr">
+        <is>
+          <t>+48 52 360 75 01</t>
+        </is>
+      </c>
+      <c r="P745" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q745" s="2" t="inlineStr">
+        <is>
+          <t>5921987110</t>
+        </is>
+      </c>
+      <c r="R745" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/farutex/</t>
+        </is>
+      </c>
+      <c r="S745" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="T745" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="U745" s="2" t="inlineStr"/>
+      <c r="V745" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCg0GPcESE_uDY_WZJITDpUw</t>
+        </is>
+      </c>
+      <c r="W745" s="2" t="inlineStr">
+        <is>
+          <t>Martyna Foremna-pitala</t>
+        </is>
+      </c>
+      <c r="X745" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager Brands Fine Wine</t>
+        </is>
+      </c>
+      <c r="Y745" s="2" t="inlineStr"/>
+      <c r="Z745" s="2" t="inlineStr"/>
+      <c r="AA745" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/martyna-foremna-pitala-57961684/</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="B746" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="C746" s="2" t="inlineStr">
+        <is>
+          <t>78034</t>
+        </is>
+      </c>
+      <c r="D746" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E746" s="2" t="inlineStr">
+        <is>
+          <t>Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="F746" s="2" t="inlineStr">
+        <is>
+          <t>Województwo kujawsko-pomorskie, Powiat Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="G746" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Mokra 30</t>
+        </is>
+      </c>
+      <c r="H746" s="2" t="inlineStr">
+        <is>
+          <t>85-834</t>
+        </is>
+      </c>
+      <c r="I746" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.pl</t>
+        </is>
+      </c>
+      <c r="J746" s="2" t="inlineStr"/>
+      <c r="K746" s="2" t="inlineStr"/>
+      <c r="L746" s="2" t="inlineStr"/>
+      <c r="M746" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N746" s="2" t="inlineStr">
+        <is>
+          <t>lmucha@bidfood.pl</t>
+        </is>
+      </c>
+      <c r="O746" s="2" t="inlineStr">
+        <is>
+          <t>+48 52 360 75 01</t>
+        </is>
+      </c>
+      <c r="P746" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q746" s="2" t="inlineStr">
+        <is>
+          <t>5921987110</t>
+        </is>
+      </c>
+      <c r="R746" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/farutex/</t>
+        </is>
+      </c>
+      <c r="S746" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="T746" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="U746" s="2" t="inlineStr"/>
+      <c r="V746" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCg0GPcESE_uDY_WZJITDpUw</t>
+        </is>
+      </c>
+      <c r="W746" s="2" t="inlineStr">
+        <is>
+          <t>Krzysztof Ligaj</t>
+        </is>
+      </c>
+      <c r="X746" s="2" t="inlineStr">
+        <is>
+          <t>Category Commercial Buyer</t>
+        </is>
+      </c>
+      <c r="Y746" s="2" t="inlineStr"/>
+      <c r="Z746" s="2" t="inlineStr"/>
+      <c r="AA746" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/krzysztof-ligaj-858998143/</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="B747" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="C747" s="2" t="inlineStr">
+        <is>
+          <t>78034</t>
+        </is>
+      </c>
+      <c r="D747" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E747" s="2" t="inlineStr">
+        <is>
+          <t>Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="F747" s="2" t="inlineStr">
+        <is>
+          <t>Województwo kujawsko-pomorskie, Powiat Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="G747" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Mokra 30</t>
+        </is>
+      </c>
+      <c r="H747" s="2" t="inlineStr">
+        <is>
+          <t>85-834</t>
+        </is>
+      </c>
+      <c r="I747" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.pl</t>
+        </is>
+      </c>
+      <c r="J747" s="2" t="inlineStr"/>
+      <c r="K747" s="2" t="inlineStr"/>
+      <c r="L747" s="2" t="inlineStr"/>
+      <c r="M747" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N747" s="2" t="inlineStr">
+        <is>
+          <t>lmucha@bidfood.pl</t>
+        </is>
+      </c>
+      <c r="O747" s="2" t="inlineStr">
+        <is>
+          <t>+48 52 360 75 01</t>
+        </is>
+      </c>
+      <c r="P747" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q747" s="2" t="inlineStr">
+        <is>
+          <t>5921987110</t>
+        </is>
+      </c>
+      <c r="R747" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/farutex/</t>
+        </is>
+      </c>
+      <c r="S747" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="T747" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="U747" s="2" t="inlineStr"/>
+      <c r="V747" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCg0GPcESE_uDY_WZJITDpUw</t>
+        </is>
+      </c>
+      <c r="W747" s="2" t="inlineStr">
+        <is>
+          <t>Magdalena Kwiecień</t>
+        </is>
+      </c>
+      <c r="X747" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Specialist</t>
+        </is>
+      </c>
+      <c r="Y747" s="2" t="inlineStr"/>
+      <c r="Z747" s="2" t="inlineStr"/>
+      <c r="AA747" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/magdalena-kwiecie%c5%84-0906b5214/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Poland.xlsx
+++ b/BWI/bestwine_output/bestwine_Poland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA747"/>
+  <dimension ref="A1:AA751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -78726,6 +78726,458 @@
         </is>
       </c>
     </row>
+    <row r="748">
+      <c r="A748" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="B748" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="C748" s="2" t="inlineStr">
+        <is>
+          <t>78034</t>
+        </is>
+      </c>
+      <c r="D748" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E748" s="2" t="inlineStr">
+        <is>
+          <t>Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="F748" s="2" t="inlineStr">
+        <is>
+          <t>Województwo kujawsko-pomorskie, Powiat Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="G748" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Mokra 30</t>
+        </is>
+      </c>
+      <c r="H748" s="2" t="inlineStr">
+        <is>
+          <t>85-834</t>
+        </is>
+      </c>
+      <c r="I748" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.pl</t>
+        </is>
+      </c>
+      <c r="J748" s="2" t="inlineStr"/>
+      <c r="K748" s="2" t="inlineStr"/>
+      <c r="L748" s="2" t="inlineStr"/>
+      <c r="M748" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N748" s="2" t="inlineStr">
+        <is>
+          <t>lmucha@bidfood.pl</t>
+        </is>
+      </c>
+      <c r="O748" s="2" t="inlineStr">
+        <is>
+          <t>+48 52 360 75 01</t>
+        </is>
+      </c>
+      <c r="P748" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q748" s="2" t="inlineStr">
+        <is>
+          <t>5921987110</t>
+        </is>
+      </c>
+      <c r="R748" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/farutex/</t>
+        </is>
+      </c>
+      <c r="S748" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="T748" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="U748" s="2" t="inlineStr"/>
+      <c r="V748" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCg0GPcESE_uDY_WZJITDpUw</t>
+        </is>
+      </c>
+      <c r="W748" s="2" t="inlineStr">
+        <is>
+          <t>Łukasz Mucha</t>
+        </is>
+      </c>
+      <c r="X748" s="2" t="inlineStr">
+        <is>
+          <t>Manager of Purchasing Department</t>
+        </is>
+      </c>
+      <c r="Y748" s="2" t="inlineStr"/>
+      <c r="Z748" s="2" t="inlineStr"/>
+      <c r="AA748" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/%C5%82ukasz-mucha-972a6596</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="B749" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="C749" s="2" t="inlineStr">
+        <is>
+          <t>78034</t>
+        </is>
+      </c>
+      <c r="D749" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E749" s="2" t="inlineStr">
+        <is>
+          <t>Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="F749" s="2" t="inlineStr">
+        <is>
+          <t>Województwo kujawsko-pomorskie, Powiat Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="G749" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Mokra 30</t>
+        </is>
+      </c>
+      <c r="H749" s="2" t="inlineStr">
+        <is>
+          <t>85-834</t>
+        </is>
+      </c>
+      <c r="I749" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.pl</t>
+        </is>
+      </c>
+      <c r="J749" s="2" t="inlineStr"/>
+      <c r="K749" s="2" t="inlineStr"/>
+      <c r="L749" s="2" t="inlineStr"/>
+      <c r="M749" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N749" s="2" t="inlineStr">
+        <is>
+          <t>lmucha@bidfood.pl</t>
+        </is>
+      </c>
+      <c r="O749" s="2" t="inlineStr">
+        <is>
+          <t>+48 52 360 75 01</t>
+        </is>
+      </c>
+      <c r="P749" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q749" s="2" t="inlineStr">
+        <is>
+          <t>5921987110</t>
+        </is>
+      </c>
+      <c r="R749" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/farutex/</t>
+        </is>
+      </c>
+      <c r="S749" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="T749" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="U749" s="2" t="inlineStr"/>
+      <c r="V749" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCg0GPcESE_uDY_WZJITDpUw</t>
+        </is>
+      </c>
+      <c r="W749" s="2" t="inlineStr">
+        <is>
+          <t>Martyna Foremna-pitala</t>
+        </is>
+      </c>
+      <c r="X749" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager Brands Fine Wine</t>
+        </is>
+      </c>
+      <c r="Y749" s="2" t="inlineStr"/>
+      <c r="Z749" s="2" t="inlineStr"/>
+      <c r="AA749" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/martyna-foremna-pitala-57961684/</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="B750" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="C750" s="2" t="inlineStr">
+        <is>
+          <t>78034</t>
+        </is>
+      </c>
+      <c r="D750" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E750" s="2" t="inlineStr">
+        <is>
+          <t>Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="F750" s="2" t="inlineStr">
+        <is>
+          <t>Województwo kujawsko-pomorskie, Powiat Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="G750" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Mokra 30</t>
+        </is>
+      </c>
+      <c r="H750" s="2" t="inlineStr">
+        <is>
+          <t>85-834</t>
+        </is>
+      </c>
+      <c r="I750" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.pl</t>
+        </is>
+      </c>
+      <c r="J750" s="2" t="inlineStr"/>
+      <c r="K750" s="2" t="inlineStr"/>
+      <c r="L750" s="2" t="inlineStr"/>
+      <c r="M750" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N750" s="2" t="inlineStr">
+        <is>
+          <t>lmucha@bidfood.pl</t>
+        </is>
+      </c>
+      <c r="O750" s="2" t="inlineStr">
+        <is>
+          <t>+48 52 360 75 01</t>
+        </is>
+      </c>
+      <c r="P750" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q750" s="2" t="inlineStr">
+        <is>
+          <t>5921987110</t>
+        </is>
+      </c>
+      <c r="R750" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/farutex/</t>
+        </is>
+      </c>
+      <c r="S750" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="T750" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="U750" s="2" t="inlineStr"/>
+      <c r="V750" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCg0GPcESE_uDY_WZJITDpUw</t>
+        </is>
+      </c>
+      <c r="W750" s="2" t="inlineStr">
+        <is>
+          <t>Krzysztof Ligaj</t>
+        </is>
+      </c>
+      <c r="X750" s="2" t="inlineStr">
+        <is>
+          <t>Category Commercial Buyer</t>
+        </is>
+      </c>
+      <c r="Y750" s="2" t="inlineStr"/>
+      <c r="Z750" s="2" t="inlineStr"/>
+      <c r="AA750" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/krzysztof-ligaj-858998143/</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="B751" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="C751" s="2" t="inlineStr">
+        <is>
+          <t>78034</t>
+        </is>
+      </c>
+      <c r="D751" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E751" s="2" t="inlineStr">
+        <is>
+          <t>Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="F751" s="2" t="inlineStr">
+        <is>
+          <t>Województwo kujawsko-pomorskie, Powiat Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="G751" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Mokra 30</t>
+        </is>
+      </c>
+      <c r="H751" s="2" t="inlineStr">
+        <is>
+          <t>85-834</t>
+        </is>
+      </c>
+      <c r="I751" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.pl</t>
+        </is>
+      </c>
+      <c r="J751" s="2" t="inlineStr"/>
+      <c r="K751" s="2" t="inlineStr"/>
+      <c r="L751" s="2" t="inlineStr"/>
+      <c r="M751" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N751" s="2" t="inlineStr">
+        <is>
+          <t>lmucha@bidfood.pl</t>
+        </is>
+      </c>
+      <c r="O751" s="2" t="inlineStr">
+        <is>
+          <t>+48 52 360 75 01</t>
+        </is>
+      </c>
+      <c r="P751" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q751" s="2" t="inlineStr">
+        <is>
+          <t>5921987110</t>
+        </is>
+      </c>
+      <c r="R751" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/farutex/</t>
+        </is>
+      </c>
+      <c r="S751" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="T751" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="U751" s="2" t="inlineStr"/>
+      <c r="V751" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCg0GPcESE_uDY_WZJITDpUw</t>
+        </is>
+      </c>
+      <c r="W751" s="2" t="inlineStr">
+        <is>
+          <t>Magdalena Kwiecień</t>
+        </is>
+      </c>
+      <c r="X751" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Specialist</t>
+        </is>
+      </c>
+      <c r="Y751" s="2" t="inlineStr"/>
+      <c r="Z751" s="2" t="inlineStr"/>
+      <c r="AA751" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/magdalena-kwiecie%c5%84-0906b5214/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Poland.xlsx
+++ b/BWI/bestwine_output/bestwine_Poland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA751"/>
+  <dimension ref="A1:AA766"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -79178,6 +79178,1661 @@
         </is>
       </c>
     </row>
+    <row r="752">
+      <c r="A752" s="2" t="inlineStr">
+        <is>
+          <t>Spar Sp. Z.o.o.</t>
+        </is>
+      </c>
+      <c r="B752" s="2" t="inlineStr">
+        <is>
+          <t>Spar Sp. Z.o.o.</t>
+        </is>
+      </c>
+      <c r="C752" s="2" t="inlineStr">
+        <is>
+          <t>108283</t>
+        </is>
+      </c>
+      <c r="D752" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E752" s="2" t="inlineStr">
+        <is>
+          <t>Poznań</t>
+        </is>
+      </c>
+      <c r="F752" s="2" t="inlineStr">
+        <is>
+          <t>Wielkopolskie</t>
+        </is>
+      </c>
+      <c r="G752" s="2" t="inlineStr">
+        <is>
+          <t>12 Druskienicka</t>
+        </is>
+      </c>
+      <c r="H752" s="2" t="inlineStr">
+        <is>
+          <t>60-476</t>
+        </is>
+      </c>
+      <c r="I752" s="2" t="inlineStr">
+        <is>
+          <t>https://e-spar.com.pl, https://spar.pl</t>
+        </is>
+      </c>
+      <c r="J752" s="2" t="inlineStr"/>
+      <c r="K752" s="2" t="inlineStr"/>
+      <c r="L752" s="2" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="M752" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N752" s="2" t="inlineStr">
+        <is>
+          <t>kontakt@spar.pl</t>
+        </is>
+      </c>
+      <c r="O752" s="2" t="inlineStr">
+        <is>
+          <t>+48 61 840 37 00</t>
+        </is>
+      </c>
+      <c r="P752" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q752" s="2" t="inlineStr">
+        <is>
+          <t>7831797536</t>
+        </is>
+      </c>
+      <c r="R752" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/spar-poland/</t>
+        </is>
+      </c>
+      <c r="S752" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sparpolskapl</t>
+        </is>
+      </c>
+      <c r="T752" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sparpolska/</t>
+        </is>
+      </c>
+      <c r="U752" s="2" t="inlineStr"/>
+      <c r="V752" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@sparpolska1096</t>
+        </is>
+      </c>
+      <c r="W752" s="2" t="inlineStr">
+        <is>
+          <t>Magdalena Błaszczak</t>
+        </is>
+      </c>
+      <c r="X752" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y752" s="2" t="inlineStr"/>
+      <c r="Z752" s="2" t="inlineStr"/>
+      <c r="AA752" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/magdalena-b%C5%82aszczak-a40244203/</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="2" t="inlineStr">
+        <is>
+          <t>Spar Sp. Z.o.o.</t>
+        </is>
+      </c>
+      <c r="B753" s="2" t="inlineStr">
+        <is>
+          <t>Spar Sp. Z.o.o.</t>
+        </is>
+      </c>
+      <c r="C753" s="2" t="inlineStr">
+        <is>
+          <t>108283</t>
+        </is>
+      </c>
+      <c r="D753" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E753" s="2" t="inlineStr">
+        <is>
+          <t>Poznań</t>
+        </is>
+      </c>
+      <c r="F753" s="2" t="inlineStr">
+        <is>
+          <t>Wielkopolskie</t>
+        </is>
+      </c>
+      <c r="G753" s="2" t="inlineStr">
+        <is>
+          <t>12 Druskienicka</t>
+        </is>
+      </c>
+      <c r="H753" s="2" t="inlineStr">
+        <is>
+          <t>60-476</t>
+        </is>
+      </c>
+      <c r="I753" s="2" t="inlineStr">
+        <is>
+          <t>https://e-spar.com.pl, https://spar.pl</t>
+        </is>
+      </c>
+      <c r="J753" s="2" t="inlineStr"/>
+      <c r="K753" s="2" t="inlineStr"/>
+      <c r="L753" s="2" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="M753" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N753" s="2" t="inlineStr">
+        <is>
+          <t>kontakt@spar.pl</t>
+        </is>
+      </c>
+      <c r="O753" s="2" t="inlineStr">
+        <is>
+          <t>+48 61 840 37 00</t>
+        </is>
+      </c>
+      <c r="P753" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q753" s="2" t="inlineStr">
+        <is>
+          <t>7831797536</t>
+        </is>
+      </c>
+      <c r="R753" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/spar-poland/</t>
+        </is>
+      </c>
+      <c r="S753" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sparpolskapl</t>
+        </is>
+      </c>
+      <c r="T753" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sparpolska/</t>
+        </is>
+      </c>
+      <c r="U753" s="2" t="inlineStr"/>
+      <c r="V753" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@sparpolska1096</t>
+        </is>
+      </c>
+      <c r="W753" s="2" t="inlineStr">
+        <is>
+          <t>Tomasz Wilkoń</t>
+        </is>
+      </c>
+      <c r="X753" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Director</t>
+        </is>
+      </c>
+      <c r="Y753" s="2" t="inlineStr"/>
+      <c r="Z753" s="2" t="inlineStr"/>
+      <c r="AA753" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tomaszwilkon/</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="2" t="inlineStr">
+        <is>
+          <t>Spar Sp. Z.o.o.</t>
+        </is>
+      </c>
+      <c r="B754" s="2" t="inlineStr">
+        <is>
+          <t>Spar Sp. Z.o.o.</t>
+        </is>
+      </c>
+      <c r="C754" s="2" t="inlineStr">
+        <is>
+          <t>108283</t>
+        </is>
+      </c>
+      <c r="D754" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E754" s="2" t="inlineStr">
+        <is>
+          <t>Poznań</t>
+        </is>
+      </c>
+      <c r="F754" s="2" t="inlineStr">
+        <is>
+          <t>Wielkopolskie</t>
+        </is>
+      </c>
+      <c r="G754" s="2" t="inlineStr">
+        <is>
+          <t>12 Druskienicka</t>
+        </is>
+      </c>
+      <c r="H754" s="2" t="inlineStr">
+        <is>
+          <t>60-476</t>
+        </is>
+      </c>
+      <c r="I754" s="2" t="inlineStr">
+        <is>
+          <t>https://e-spar.com.pl, https://spar.pl</t>
+        </is>
+      </c>
+      <c r="J754" s="2" t="inlineStr"/>
+      <c r="K754" s="2" t="inlineStr"/>
+      <c r="L754" s="2" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="M754" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N754" s="2" t="inlineStr">
+        <is>
+          <t>kontakt@spar.pl</t>
+        </is>
+      </c>
+      <c r="O754" s="2" t="inlineStr">
+        <is>
+          <t>+48 61 840 37 00</t>
+        </is>
+      </c>
+      <c r="P754" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q754" s="2" t="inlineStr">
+        <is>
+          <t>7831797536</t>
+        </is>
+      </c>
+      <c r="R754" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/spar-poland/</t>
+        </is>
+      </c>
+      <c r="S754" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sparpolskapl</t>
+        </is>
+      </c>
+      <c r="T754" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sparpolska/</t>
+        </is>
+      </c>
+      <c r="U754" s="2" t="inlineStr"/>
+      <c r="V754" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@sparpolska1096</t>
+        </is>
+      </c>
+      <c r="W754" s="2" t="inlineStr">
+        <is>
+          <t>Jacek Ostrowski</t>
+        </is>
+      </c>
+      <c r="X754" s="2" t="inlineStr">
+        <is>
+          <t>Merchant/ Buyer</t>
+        </is>
+      </c>
+      <c r="Y754" s="2" t="inlineStr"/>
+      <c r="Z754" s="2" t="inlineStr"/>
+      <c r="AA754" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jacek-ostrowski-5103ab4b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="2" t="inlineStr">
+        <is>
+          <t>The Wine House Sp. Z O. O.</t>
+        </is>
+      </c>
+      <c r="B755" s="2" t="inlineStr">
+        <is>
+          <t>The Wine House Sp. Z O. O.</t>
+        </is>
+      </c>
+      <c r="C755" s="2" t="inlineStr">
+        <is>
+          <t>121873</t>
+        </is>
+      </c>
+      <c r="D755" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E755" s="2" t="inlineStr">
+        <is>
+          <t>Warszawa</t>
+        </is>
+      </c>
+      <c r="F755" s="2" t="inlineStr">
+        <is>
+          <t>Województwo mazowieckie, Powiat Warszawa</t>
+        </is>
+      </c>
+      <c r="G755" s="2" t="inlineStr">
+        <is>
+          <t>83 Ludwika Narbutta</t>
+        </is>
+      </c>
+      <c r="H755" s="2" t="inlineStr">
+        <is>
+          <t>02-524</t>
+        </is>
+      </c>
+      <c r="I755" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thewinehouse.pl</t>
+        </is>
+      </c>
+      <c r="J755" s="2" t="inlineStr"/>
+      <c r="K755" s="2" t="inlineStr"/>
+      <c r="L755" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M755" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N755" s="2" t="inlineStr">
+        <is>
+          <t>info@thewinehouse.pl</t>
+        </is>
+      </c>
+      <c r="O755" s="2" t="inlineStr"/>
+      <c r="P755" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q755" s="2" t="inlineStr">
+        <is>
+          <t>5342627035</t>
+        </is>
+      </c>
+      <c r="R755" s="2" t="inlineStr"/>
+      <c r="S755" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TheWineHousePoland</t>
+        </is>
+      </c>
+      <c r="T755" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/the__wine__house/</t>
+        </is>
+      </c>
+      <c r="U755" s="2" t="inlineStr"/>
+      <c r="V755" s="2" t="inlineStr"/>
+      <c r="W755" s="2" t="inlineStr"/>
+      <c r="X755" s="2" t="inlineStr"/>
+      <c r="Y755" s="2" t="inlineStr"/>
+      <c r="Z755" s="2" t="inlineStr"/>
+      <c r="AA755" s="2" t="inlineStr"/>
+    </row>
+    <row r="756">
+      <c r="A756" s="2" t="inlineStr">
+        <is>
+          <t>Wine &amp; Style Franck Encina</t>
+        </is>
+      </c>
+      <c r="B756" s="2" t="inlineStr">
+        <is>
+          <t>Wine &amp; Style Franck Encina</t>
+        </is>
+      </c>
+      <c r="C756" s="2" t="inlineStr">
+        <is>
+          <t>121822</t>
+        </is>
+      </c>
+      <c r="D756" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E756" s="2" t="inlineStr">
+        <is>
+          <t>Warszawa</t>
+        </is>
+      </c>
+      <c r="F756" s="2" t="inlineStr">
+        <is>
+          <t>Mazowieckie</t>
+        </is>
+      </c>
+      <c r="G756" s="2" t="inlineStr">
+        <is>
+          <t>95 Łopuszańska</t>
+        </is>
+      </c>
+      <c r="H756" s="2" t="inlineStr">
+        <is>
+          <t>02-457</t>
+        </is>
+      </c>
+      <c r="I756" s="2" t="inlineStr">
+        <is>
+          <t>https://wineandstyle.pl</t>
+        </is>
+      </c>
+      <c r="J756" s="2" t="inlineStr"/>
+      <c r="K756" s="2" t="inlineStr"/>
+      <c r="L756" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M756" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N756" s="2" t="inlineStr">
+        <is>
+          <t>kontakt@wineandstyle.pl</t>
+        </is>
+      </c>
+      <c r="O756" s="2" t="inlineStr"/>
+      <c r="P756" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q756" s="2" t="inlineStr">
+        <is>
+          <t>5222880866</t>
+        </is>
+      </c>
+      <c r="R756" s="2" t="inlineStr"/>
+      <c r="S756" s="2" t="inlineStr"/>
+      <c r="T756" s="2" t="inlineStr"/>
+      <c r="U756" s="2" t="inlineStr"/>
+      <c r="V756" s="2" t="inlineStr"/>
+      <c r="W756" s="2" t="inlineStr">
+        <is>
+          <t>Frank Encina</t>
+        </is>
+      </c>
+      <c r="X756" s="2" t="inlineStr">
+        <is>
+          <t>Wine Importer &amp; Distributor</t>
+        </is>
+      </c>
+      <c r="Y756" s="2" t="inlineStr"/>
+      <c r="Z756" s="2" t="inlineStr"/>
+      <c r="AA756" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/frank-encina-97ab9731/</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="2" t="inlineStr">
+        <is>
+          <t>Winnice Francji Sp Z O O</t>
+        </is>
+      </c>
+      <c r="B757" s="2" t="inlineStr">
+        <is>
+          <t>Winnice Francji Sp Z O O</t>
+        </is>
+      </c>
+      <c r="C757" s="2" t="inlineStr">
+        <is>
+          <t>54933</t>
+        </is>
+      </c>
+      <c r="D757" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E757" s="2" t="inlineStr">
+        <is>
+          <t>Kraków</t>
+        </is>
+      </c>
+      <c r="F757" s="2" t="inlineStr">
+        <is>
+          <t>Małopolskie</t>
+        </is>
+      </c>
+      <c r="G757" s="2" t="inlineStr">
+        <is>
+          <t>17 Tadeusza Romanowicza</t>
+        </is>
+      </c>
+      <c r="H757" s="2" t="inlineStr">
+        <is>
+          <t>30-702</t>
+        </is>
+      </c>
+      <c r="I757" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winnicefrancji.pl</t>
+        </is>
+      </c>
+      <c r="J757" s="2" t="inlineStr"/>
+      <c r="K757" s="2" t="inlineStr"/>
+      <c r="L757" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M757" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N757" s="2" t="inlineStr">
+        <is>
+          <t>epariselle@winnicefrancji.pl</t>
+        </is>
+      </c>
+      <c r="O757" s="2" t="inlineStr"/>
+      <c r="P757" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q757" s="2" t="inlineStr">
+        <is>
+          <t>7251002158</t>
+        </is>
+      </c>
+      <c r="R757" s="2" t="inlineStr"/>
+      <c r="S757" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WinaZFrancji</t>
+        </is>
+      </c>
+      <c r="T757" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winnice_francji/</t>
+        </is>
+      </c>
+      <c r="U757" s="2" t="inlineStr"/>
+      <c r="V757" s="2" t="inlineStr"/>
+      <c r="W757" s="2" t="inlineStr">
+        <is>
+          <t>Beata Pieczko</t>
+        </is>
+      </c>
+      <c r="X757" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y757" s="2" t="inlineStr"/>
+      <c r="Z757" s="2" t="inlineStr"/>
+      <c r="AA757" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/beata-pieczko-1135086/</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="2" t="inlineStr">
+        <is>
+          <t>Lewiatan Holding S A</t>
+        </is>
+      </c>
+      <c r="B758" s="2" t="inlineStr">
+        <is>
+          <t>Lewiatan Holding S A</t>
+        </is>
+      </c>
+      <c r="C758" s="2" t="inlineStr">
+        <is>
+          <t>78224</t>
+        </is>
+      </c>
+      <c r="D758" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E758" s="2" t="inlineStr">
+        <is>
+          <t>Włocławek</t>
+        </is>
+      </c>
+      <c r="F758" s="2" t="inlineStr">
+        <is>
+          <t>Województwo kujawsko-pomorskie, Powiat Włocławek</t>
+        </is>
+      </c>
+      <c r="G758" s="2" t="inlineStr">
+        <is>
+          <t>10 Jana Kilińskiego</t>
+        </is>
+      </c>
+      <c r="H758" s="2" t="inlineStr">
+        <is>
+          <t>87-800</t>
+        </is>
+      </c>
+      <c r="I758" s="2" t="inlineStr">
+        <is>
+          <t>https://lewiatan.pl</t>
+        </is>
+      </c>
+      <c r="J758" s="2" t="inlineStr"/>
+      <c r="K758" s="2" t="inlineStr"/>
+      <c r="L758" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="M758" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N758" s="2" t="inlineStr">
+        <is>
+          <t>robert.rekas@lewiatan.pl</t>
+        </is>
+      </c>
+      <c r="O758" s="2" t="inlineStr">
+        <is>
+          <t>+48 54 412 78 21</t>
+        </is>
+      </c>
+      <c r="P758" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q758" s="2" t="inlineStr">
+        <is>
+          <t>6181020505</t>
+        </is>
+      </c>
+      <c r="R758" s="2" t="inlineStr"/>
+      <c r="S758" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/psh.lewiatan/</t>
+        </is>
+      </c>
+      <c r="T758" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lewiatanlubelskie/</t>
+        </is>
+      </c>
+      <c r="U758" s="2" t="inlineStr"/>
+      <c r="V758" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PSHLewiatan/f</t>
+        </is>
+      </c>
+      <c r="W758" s="2" t="inlineStr">
+        <is>
+          <t>Artur Ratajczyk</t>
+        </is>
+      </c>
+      <c r="X758" s="2" t="inlineStr">
+        <is>
+          <t>Senior Merchant</t>
+        </is>
+      </c>
+      <c r="Y758" s="2" t="inlineStr"/>
+      <c r="Z758" s="2" t="inlineStr"/>
+      <c r="AA758" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/artur-ratajczyk-23a28a217/</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="2" t="inlineStr">
+        <is>
+          <t>Lewiatan Holding S A</t>
+        </is>
+      </c>
+      <c r="B759" s="2" t="inlineStr">
+        <is>
+          <t>Lewiatan Holding S A</t>
+        </is>
+      </c>
+      <c r="C759" s="2" t="inlineStr">
+        <is>
+          <t>78224</t>
+        </is>
+      </c>
+      <c r="D759" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E759" s="2" t="inlineStr">
+        <is>
+          <t>Włocławek</t>
+        </is>
+      </c>
+      <c r="F759" s="2" t="inlineStr">
+        <is>
+          <t>Województwo kujawsko-pomorskie, Powiat Włocławek</t>
+        </is>
+      </c>
+      <c r="G759" s="2" t="inlineStr">
+        <is>
+          <t>10 Jana Kilińskiego</t>
+        </is>
+      </c>
+      <c r="H759" s="2" t="inlineStr">
+        <is>
+          <t>87-800</t>
+        </is>
+      </c>
+      <c r="I759" s="2" t="inlineStr">
+        <is>
+          <t>https://lewiatan.pl</t>
+        </is>
+      </c>
+      <c r="J759" s="2" t="inlineStr"/>
+      <c r="K759" s="2" t="inlineStr"/>
+      <c r="L759" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="M759" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N759" s="2" t="inlineStr">
+        <is>
+          <t>robert.rekas@lewiatan.pl</t>
+        </is>
+      </c>
+      <c r="O759" s="2" t="inlineStr">
+        <is>
+          <t>+48 54 412 78 21</t>
+        </is>
+      </c>
+      <c r="P759" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q759" s="2" t="inlineStr">
+        <is>
+          <t>6181020505</t>
+        </is>
+      </c>
+      <c r="R759" s="2" t="inlineStr"/>
+      <c r="S759" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/psh.lewiatan/</t>
+        </is>
+      </c>
+      <c r="T759" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lewiatanlubelskie/</t>
+        </is>
+      </c>
+      <c r="U759" s="2" t="inlineStr"/>
+      <c r="V759" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PSHLewiatan/f</t>
+        </is>
+      </c>
+      <c r="W759" s="2" t="inlineStr">
+        <is>
+          <t>Katarzyna Zaborowicz</t>
+        </is>
+      </c>
+      <c r="X759" s="2" t="inlineStr">
+        <is>
+          <t>National Category Group Management Manager</t>
+        </is>
+      </c>
+      <c r="Y759" s="2" t="inlineStr"/>
+      <c r="Z759" s="2" t="inlineStr"/>
+      <c r="AA759" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/katarzyna-zaborowicz-584bb5186/</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="2" t="inlineStr">
+        <is>
+          <t>Lewiatan Holding S A</t>
+        </is>
+      </c>
+      <c r="B760" s="2" t="inlineStr">
+        <is>
+          <t>Lewiatan Holding S A</t>
+        </is>
+      </c>
+      <c r="C760" s="2" t="inlineStr">
+        <is>
+          <t>78224</t>
+        </is>
+      </c>
+      <c r="D760" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E760" s="2" t="inlineStr">
+        <is>
+          <t>Włocławek</t>
+        </is>
+      </c>
+      <c r="F760" s="2" t="inlineStr">
+        <is>
+          <t>Województwo kujawsko-pomorskie, Powiat Włocławek</t>
+        </is>
+      </c>
+      <c r="G760" s="2" t="inlineStr">
+        <is>
+          <t>10 Jana Kilińskiego</t>
+        </is>
+      </c>
+      <c r="H760" s="2" t="inlineStr">
+        <is>
+          <t>87-800</t>
+        </is>
+      </c>
+      <c r="I760" s="2" t="inlineStr">
+        <is>
+          <t>https://lewiatan.pl</t>
+        </is>
+      </c>
+      <c r="J760" s="2" t="inlineStr"/>
+      <c r="K760" s="2" t="inlineStr"/>
+      <c r="L760" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="M760" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N760" s="2" t="inlineStr">
+        <is>
+          <t>robert.rekas@lewiatan.pl</t>
+        </is>
+      </c>
+      <c r="O760" s="2" t="inlineStr">
+        <is>
+          <t>+48 54 412 78 21</t>
+        </is>
+      </c>
+      <c r="P760" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q760" s="2" t="inlineStr">
+        <is>
+          <t>6181020505</t>
+        </is>
+      </c>
+      <c r="R760" s="2" t="inlineStr"/>
+      <c r="S760" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/psh.lewiatan/</t>
+        </is>
+      </c>
+      <c r="T760" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lewiatanlubelskie/</t>
+        </is>
+      </c>
+      <c r="U760" s="2" t="inlineStr"/>
+      <c r="V760" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PSHLewiatan/f</t>
+        </is>
+      </c>
+      <c r="W760" s="2" t="inlineStr">
+        <is>
+          <t>Robert Rękas</t>
+        </is>
+      </c>
+      <c r="X760" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y760" s="2" t="inlineStr"/>
+      <c r="Z760" s="2" t="inlineStr"/>
+      <c r="AA760" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/robert-r%C4%99kas-959b51113/</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="2" t="inlineStr">
+        <is>
+          <t>Arhelan Sp Z O O</t>
+        </is>
+      </c>
+      <c r="B761" s="2" t="inlineStr">
+        <is>
+          <t>Arhelan Sp Z O O</t>
+        </is>
+      </c>
+      <c r="C761" s="2" t="inlineStr">
+        <is>
+          <t>11229</t>
+        </is>
+      </c>
+      <c r="D761" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E761" s="2" t="inlineStr">
+        <is>
+          <t>Bielsk Podlaski</t>
+        </is>
+      </c>
+      <c r="F761" s="2" t="inlineStr">
+        <is>
+          <t>Województwo podlaskie, Powiat bielski</t>
+        </is>
+      </c>
+      <c r="G761" s="2" t="inlineStr">
+        <is>
+          <t>45 Al. Józefa Piłsudskiego</t>
+        </is>
+      </c>
+      <c r="H761" s="2" t="inlineStr">
+        <is>
+          <t>17-100</t>
+        </is>
+      </c>
+      <c r="I761" s="2" t="inlineStr">
+        <is>
+          <t>https://arhelan.pl</t>
+        </is>
+      </c>
+      <c r="J761" s="2" t="inlineStr"/>
+      <c r="K761" s="2" t="inlineStr"/>
+      <c r="L761" s="2" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="M761" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N761" s="2" t="inlineStr">
+        <is>
+          <t>agnieszka.kindziuk@arhelan.pl</t>
+        </is>
+      </c>
+      <c r="O761" s="2" t="inlineStr">
+        <is>
+          <t>+48 85 730 20 03</t>
+        </is>
+      </c>
+      <c r="P761" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q761" s="2" t="inlineStr">
+        <is>
+          <t>5430001447</t>
+        </is>
+      </c>
+      <c r="R761" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/arhelan-burzy%C5%84scy-sp-j/</t>
+        </is>
+      </c>
+      <c r="S761" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SklepyArhelan/</t>
+        </is>
+      </c>
+      <c r="T761" s="2" t="inlineStr"/>
+      <c r="U761" s="2" t="inlineStr"/>
+      <c r="V761" s="2" t="inlineStr"/>
+      <c r="W761" s="2" t="inlineStr">
+        <is>
+          <t>Joanna Namojlik</t>
+        </is>
+      </c>
+      <c r="X761" s="2" t="inlineStr">
+        <is>
+          <t>Regional Operations Manager</t>
+        </is>
+      </c>
+      <c r="Y761" s="2" t="inlineStr"/>
+      <c r="Z761" s="2" t="inlineStr"/>
+      <c r="AA761" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/joanna-namojlik-439b16280/</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="2" t="inlineStr">
+        <is>
+          <t>Arhelan Sp Z O O</t>
+        </is>
+      </c>
+      <c r="B762" s="2" t="inlineStr">
+        <is>
+          <t>Arhelan Sp Z O O</t>
+        </is>
+      </c>
+      <c r="C762" s="2" t="inlineStr">
+        <is>
+          <t>11229</t>
+        </is>
+      </c>
+      <c r="D762" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E762" s="2" t="inlineStr">
+        <is>
+          <t>Bielsk Podlaski</t>
+        </is>
+      </c>
+      <c r="F762" s="2" t="inlineStr">
+        <is>
+          <t>Województwo podlaskie, Powiat bielski</t>
+        </is>
+      </c>
+      <c r="G762" s="2" t="inlineStr">
+        <is>
+          <t>45 Al. Józefa Piłsudskiego</t>
+        </is>
+      </c>
+      <c r="H762" s="2" t="inlineStr">
+        <is>
+          <t>17-100</t>
+        </is>
+      </c>
+      <c r="I762" s="2" t="inlineStr">
+        <is>
+          <t>https://arhelan.pl</t>
+        </is>
+      </c>
+      <c r="J762" s="2" t="inlineStr"/>
+      <c r="K762" s="2" t="inlineStr"/>
+      <c r="L762" s="2" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="M762" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N762" s="2" t="inlineStr">
+        <is>
+          <t>agnieszka.kindziuk@arhelan.pl</t>
+        </is>
+      </c>
+      <c r="O762" s="2" t="inlineStr">
+        <is>
+          <t>+48 85 730 20 03</t>
+        </is>
+      </c>
+      <c r="P762" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q762" s="2" t="inlineStr">
+        <is>
+          <t>5430001447</t>
+        </is>
+      </c>
+      <c r="R762" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/arhelan-burzy%C5%84scy-sp-j/</t>
+        </is>
+      </c>
+      <c r="S762" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SklepyArhelan/</t>
+        </is>
+      </c>
+      <c r="T762" s="2" t="inlineStr"/>
+      <c r="U762" s="2" t="inlineStr"/>
+      <c r="V762" s="2" t="inlineStr"/>
+      <c r="W762" s="2" t="inlineStr">
+        <is>
+          <t>Agnieszka Kindziuk</t>
+        </is>
+      </c>
+      <c r="X762" s="2" t="inlineStr">
+        <is>
+          <t>Deputy Sales Director</t>
+        </is>
+      </c>
+      <c r="Y762" s="2" t="inlineStr"/>
+      <c r="Z762" s="2" t="inlineStr"/>
+      <c r="AA762" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/agnieszka-kindziuk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="B763" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="C763" s="2" t="inlineStr">
+        <is>
+          <t>78034</t>
+        </is>
+      </c>
+      <c r="D763" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E763" s="2" t="inlineStr">
+        <is>
+          <t>Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="F763" s="2" t="inlineStr">
+        <is>
+          <t>Województwo kujawsko-pomorskie, Powiat Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="G763" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Mokra 30</t>
+        </is>
+      </c>
+      <c r="H763" s="2" t="inlineStr">
+        <is>
+          <t>85-834</t>
+        </is>
+      </c>
+      <c r="I763" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.pl</t>
+        </is>
+      </c>
+      <c r="J763" s="2" t="inlineStr"/>
+      <c r="K763" s="2" t="inlineStr"/>
+      <c r="L763" s="2" t="inlineStr"/>
+      <c r="M763" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N763" s="2" t="inlineStr">
+        <is>
+          <t>lmucha@bidfood.pl</t>
+        </is>
+      </c>
+      <c r="O763" s="2" t="inlineStr">
+        <is>
+          <t>+48 52 360 75 01</t>
+        </is>
+      </c>
+      <c r="P763" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q763" s="2" t="inlineStr">
+        <is>
+          <t>5921987110</t>
+        </is>
+      </c>
+      <c r="R763" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/farutex/</t>
+        </is>
+      </c>
+      <c r="S763" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="T763" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="U763" s="2" t="inlineStr"/>
+      <c r="V763" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCg0GPcESE_uDY_WZJITDpUw</t>
+        </is>
+      </c>
+      <c r="W763" s="2" t="inlineStr">
+        <is>
+          <t>Łukasz Mucha</t>
+        </is>
+      </c>
+      <c r="X763" s="2" t="inlineStr">
+        <is>
+          <t>Manager of Purchasing Department</t>
+        </is>
+      </c>
+      <c r="Y763" s="2" t="inlineStr"/>
+      <c r="Z763" s="2" t="inlineStr"/>
+      <c r="AA763" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/%C5%82ukasz-mucha-972a6596</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="B764" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="C764" s="2" t="inlineStr">
+        <is>
+          <t>78034</t>
+        </is>
+      </c>
+      <c r="D764" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E764" s="2" t="inlineStr">
+        <is>
+          <t>Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="F764" s="2" t="inlineStr">
+        <is>
+          <t>Województwo kujawsko-pomorskie, Powiat Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="G764" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Mokra 30</t>
+        </is>
+      </c>
+      <c r="H764" s="2" t="inlineStr">
+        <is>
+          <t>85-834</t>
+        </is>
+      </c>
+      <c r="I764" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.pl</t>
+        </is>
+      </c>
+      <c r="J764" s="2" t="inlineStr"/>
+      <c r="K764" s="2" t="inlineStr"/>
+      <c r="L764" s="2" t="inlineStr"/>
+      <c r="M764" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N764" s="2" t="inlineStr">
+        <is>
+          <t>lmucha@bidfood.pl</t>
+        </is>
+      </c>
+      <c r="O764" s="2" t="inlineStr">
+        <is>
+          <t>+48 52 360 75 01</t>
+        </is>
+      </c>
+      <c r="P764" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q764" s="2" t="inlineStr">
+        <is>
+          <t>5921987110</t>
+        </is>
+      </c>
+      <c r="R764" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/farutex/</t>
+        </is>
+      </c>
+      <c r="S764" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="T764" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="U764" s="2" t="inlineStr"/>
+      <c r="V764" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCg0GPcESE_uDY_WZJITDpUw</t>
+        </is>
+      </c>
+      <c r="W764" s="2" t="inlineStr">
+        <is>
+          <t>Martyna Foremna-pitala</t>
+        </is>
+      </c>
+      <c r="X764" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager Brands Fine Wine</t>
+        </is>
+      </c>
+      <c r="Y764" s="2" t="inlineStr"/>
+      <c r="Z764" s="2" t="inlineStr"/>
+      <c r="AA764" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/martyna-foremna-pitala-57961684/</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="B765" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="C765" s="2" t="inlineStr">
+        <is>
+          <t>78034</t>
+        </is>
+      </c>
+      <c r="D765" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E765" s="2" t="inlineStr">
+        <is>
+          <t>Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="F765" s="2" t="inlineStr">
+        <is>
+          <t>Województwo kujawsko-pomorskie, Powiat Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="G765" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Mokra 30</t>
+        </is>
+      </c>
+      <c r="H765" s="2" t="inlineStr">
+        <is>
+          <t>85-834</t>
+        </is>
+      </c>
+      <c r="I765" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.pl</t>
+        </is>
+      </c>
+      <c r="J765" s="2" t="inlineStr"/>
+      <c r="K765" s="2" t="inlineStr"/>
+      <c r="L765" s="2" t="inlineStr"/>
+      <c r="M765" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N765" s="2" t="inlineStr">
+        <is>
+          <t>lmucha@bidfood.pl</t>
+        </is>
+      </c>
+      <c r="O765" s="2" t="inlineStr">
+        <is>
+          <t>+48 52 360 75 01</t>
+        </is>
+      </c>
+      <c r="P765" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q765" s="2" t="inlineStr">
+        <is>
+          <t>5921987110</t>
+        </is>
+      </c>
+      <c r="R765" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/farutex/</t>
+        </is>
+      </c>
+      <c r="S765" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="T765" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="U765" s="2" t="inlineStr"/>
+      <c r="V765" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCg0GPcESE_uDY_WZJITDpUw</t>
+        </is>
+      </c>
+      <c r="W765" s="2" t="inlineStr">
+        <is>
+          <t>Krzysztof Ligaj</t>
+        </is>
+      </c>
+      <c r="X765" s="2" t="inlineStr">
+        <is>
+          <t>Category Commercial Buyer</t>
+        </is>
+      </c>
+      <c r="Y765" s="2" t="inlineStr"/>
+      <c r="Z765" s="2" t="inlineStr"/>
+      <c r="AA765" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/krzysztof-ligaj-858998143/</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="B766" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="C766" s="2" t="inlineStr">
+        <is>
+          <t>78034</t>
+        </is>
+      </c>
+      <c r="D766" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E766" s="2" t="inlineStr">
+        <is>
+          <t>Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="F766" s="2" t="inlineStr">
+        <is>
+          <t>Województwo kujawsko-pomorskie, Powiat Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="G766" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Mokra 30</t>
+        </is>
+      </c>
+      <c r="H766" s="2" t="inlineStr">
+        <is>
+          <t>85-834</t>
+        </is>
+      </c>
+      <c r="I766" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.pl</t>
+        </is>
+      </c>
+      <c r="J766" s="2" t="inlineStr"/>
+      <c r="K766" s="2" t="inlineStr"/>
+      <c r="L766" s="2" t="inlineStr"/>
+      <c r="M766" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N766" s="2" t="inlineStr">
+        <is>
+          <t>lmucha@bidfood.pl</t>
+        </is>
+      </c>
+      <c r="O766" s="2" t="inlineStr">
+        <is>
+          <t>+48 52 360 75 01</t>
+        </is>
+      </c>
+      <c r="P766" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q766" s="2" t="inlineStr">
+        <is>
+          <t>5921987110</t>
+        </is>
+      </c>
+      <c r="R766" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/farutex/</t>
+        </is>
+      </c>
+      <c r="S766" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="T766" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="U766" s="2" t="inlineStr"/>
+      <c r="V766" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCg0GPcESE_uDY_WZJITDpUw</t>
+        </is>
+      </c>
+      <c r="W766" s="2" t="inlineStr">
+        <is>
+          <t>Magdalena Kwiecień</t>
+        </is>
+      </c>
+      <c r="X766" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Specialist</t>
+        </is>
+      </c>
+      <c r="Y766" s="2" t="inlineStr"/>
+      <c r="Z766" s="2" t="inlineStr"/>
+      <c r="AA766" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/magdalena-kwiecie%c5%84-0906b5214/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Poland.xlsx
+++ b/BWI/bestwine_output/bestwine_Poland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA766"/>
+  <dimension ref="A1:AA781"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -80833,6 +80833,1661 @@
         </is>
       </c>
     </row>
+    <row r="767">
+      <c r="A767" s="2" t="inlineStr">
+        <is>
+          <t>Spar Sp. Z.o.o.</t>
+        </is>
+      </c>
+      <c r="B767" s="2" t="inlineStr">
+        <is>
+          <t>Spar Sp. Z.o.o.</t>
+        </is>
+      </c>
+      <c r="C767" s="2" t="inlineStr">
+        <is>
+          <t>108283</t>
+        </is>
+      </c>
+      <c r="D767" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E767" s="2" t="inlineStr">
+        <is>
+          <t>Poznań</t>
+        </is>
+      </c>
+      <c r="F767" s="2" t="inlineStr">
+        <is>
+          <t>Wielkopolskie</t>
+        </is>
+      </c>
+      <c r="G767" s="2" t="inlineStr">
+        <is>
+          <t>12 Druskienicka</t>
+        </is>
+      </c>
+      <c r="H767" s="2" t="inlineStr">
+        <is>
+          <t>60-476</t>
+        </is>
+      </c>
+      <c r="I767" s="2" t="inlineStr">
+        <is>
+          <t>https://e-spar.com.pl, https://spar.pl</t>
+        </is>
+      </c>
+      <c r="J767" s="2" t="inlineStr"/>
+      <c r="K767" s="2" t="inlineStr"/>
+      <c r="L767" s="2" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="M767" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N767" s="2" t="inlineStr">
+        <is>
+          <t>kontakt@spar.pl</t>
+        </is>
+      </c>
+      <c r="O767" s="2" t="inlineStr">
+        <is>
+          <t>+48 61 840 37 00</t>
+        </is>
+      </c>
+      <c r="P767" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q767" s="2" t="inlineStr">
+        <is>
+          <t>7831797536</t>
+        </is>
+      </c>
+      <c r="R767" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/spar-poland/</t>
+        </is>
+      </c>
+      <c r="S767" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sparpolskapl</t>
+        </is>
+      </c>
+      <c r="T767" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sparpolska/</t>
+        </is>
+      </c>
+      <c r="U767" s="2" t="inlineStr"/>
+      <c r="V767" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@sparpolska1096</t>
+        </is>
+      </c>
+      <c r="W767" s="2" t="inlineStr">
+        <is>
+          <t>Magdalena Błaszczak</t>
+        </is>
+      </c>
+      <c r="X767" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y767" s="2" t="inlineStr"/>
+      <c r="Z767" s="2" t="inlineStr"/>
+      <c r="AA767" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/magdalena-b%C5%82aszczak-a40244203/</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="2" t="inlineStr">
+        <is>
+          <t>Spar Sp. Z.o.o.</t>
+        </is>
+      </c>
+      <c r="B768" s="2" t="inlineStr">
+        <is>
+          <t>Spar Sp. Z.o.o.</t>
+        </is>
+      </c>
+      <c r="C768" s="2" t="inlineStr">
+        <is>
+          <t>108283</t>
+        </is>
+      </c>
+      <c r="D768" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E768" s="2" t="inlineStr">
+        <is>
+          <t>Poznań</t>
+        </is>
+      </c>
+      <c r="F768" s="2" t="inlineStr">
+        <is>
+          <t>Wielkopolskie</t>
+        </is>
+      </c>
+      <c r="G768" s="2" t="inlineStr">
+        <is>
+          <t>12 Druskienicka</t>
+        </is>
+      </c>
+      <c r="H768" s="2" t="inlineStr">
+        <is>
+          <t>60-476</t>
+        </is>
+      </c>
+      <c r="I768" s="2" t="inlineStr">
+        <is>
+          <t>https://e-spar.com.pl, https://spar.pl</t>
+        </is>
+      </c>
+      <c r="J768" s="2" t="inlineStr"/>
+      <c r="K768" s="2" t="inlineStr"/>
+      <c r="L768" s="2" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="M768" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N768" s="2" t="inlineStr">
+        <is>
+          <t>kontakt@spar.pl</t>
+        </is>
+      </c>
+      <c r="O768" s="2" t="inlineStr">
+        <is>
+          <t>+48 61 840 37 00</t>
+        </is>
+      </c>
+      <c r="P768" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q768" s="2" t="inlineStr">
+        <is>
+          <t>7831797536</t>
+        </is>
+      </c>
+      <c r="R768" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/spar-poland/</t>
+        </is>
+      </c>
+      <c r="S768" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sparpolskapl</t>
+        </is>
+      </c>
+      <c r="T768" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sparpolska/</t>
+        </is>
+      </c>
+      <c r="U768" s="2" t="inlineStr"/>
+      <c r="V768" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@sparpolska1096</t>
+        </is>
+      </c>
+      <c r="W768" s="2" t="inlineStr">
+        <is>
+          <t>Tomasz Wilkoń</t>
+        </is>
+      </c>
+      <c r="X768" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Director</t>
+        </is>
+      </c>
+      <c r="Y768" s="2" t="inlineStr"/>
+      <c r="Z768" s="2" t="inlineStr"/>
+      <c r="AA768" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tomaszwilkon/</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="2" t="inlineStr">
+        <is>
+          <t>Spar Sp. Z.o.o.</t>
+        </is>
+      </c>
+      <c r="B769" s="2" t="inlineStr">
+        <is>
+          <t>Spar Sp. Z.o.o.</t>
+        </is>
+      </c>
+      <c r="C769" s="2" t="inlineStr">
+        <is>
+          <t>108283</t>
+        </is>
+      </c>
+      <c r="D769" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E769" s="2" t="inlineStr">
+        <is>
+          <t>Poznań</t>
+        </is>
+      </c>
+      <c r="F769" s="2" t="inlineStr">
+        <is>
+          <t>Wielkopolskie</t>
+        </is>
+      </c>
+      <c r="G769" s="2" t="inlineStr">
+        <is>
+          <t>12 Druskienicka</t>
+        </is>
+      </c>
+      <c r="H769" s="2" t="inlineStr">
+        <is>
+          <t>60-476</t>
+        </is>
+      </c>
+      <c r="I769" s="2" t="inlineStr">
+        <is>
+          <t>https://e-spar.com.pl, https://spar.pl</t>
+        </is>
+      </c>
+      <c r="J769" s="2" t="inlineStr"/>
+      <c r="K769" s="2" t="inlineStr"/>
+      <c r="L769" s="2" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="M769" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N769" s="2" t="inlineStr">
+        <is>
+          <t>kontakt@spar.pl</t>
+        </is>
+      </c>
+      <c r="O769" s="2" t="inlineStr">
+        <is>
+          <t>+48 61 840 37 00</t>
+        </is>
+      </c>
+      <c r="P769" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q769" s="2" t="inlineStr">
+        <is>
+          <t>7831797536</t>
+        </is>
+      </c>
+      <c r="R769" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/spar-poland/</t>
+        </is>
+      </c>
+      <c r="S769" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sparpolskapl</t>
+        </is>
+      </c>
+      <c r="T769" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sparpolska/</t>
+        </is>
+      </c>
+      <c r="U769" s="2" t="inlineStr"/>
+      <c r="V769" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@sparpolska1096</t>
+        </is>
+      </c>
+      <c r="W769" s="2" t="inlineStr">
+        <is>
+          <t>Jacek Ostrowski</t>
+        </is>
+      </c>
+      <c r="X769" s="2" t="inlineStr">
+        <is>
+          <t>Merchant/ Buyer</t>
+        </is>
+      </c>
+      <c r="Y769" s="2" t="inlineStr"/>
+      <c r="Z769" s="2" t="inlineStr"/>
+      <c r="AA769" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jacek-ostrowski-5103ab4b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="2" t="inlineStr">
+        <is>
+          <t>The Wine House Sp. Z O. O.</t>
+        </is>
+      </c>
+      <c r="B770" s="2" t="inlineStr">
+        <is>
+          <t>The Wine House Sp. Z O. O.</t>
+        </is>
+      </c>
+      <c r="C770" s="2" t="inlineStr">
+        <is>
+          <t>121873</t>
+        </is>
+      </c>
+      <c r="D770" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E770" s="2" t="inlineStr">
+        <is>
+          <t>Warszawa</t>
+        </is>
+      </c>
+      <c r="F770" s="2" t="inlineStr">
+        <is>
+          <t>Województwo mazowieckie, Powiat Warszawa</t>
+        </is>
+      </c>
+      <c r="G770" s="2" t="inlineStr">
+        <is>
+          <t>83 Ludwika Narbutta</t>
+        </is>
+      </c>
+      <c r="H770" s="2" t="inlineStr">
+        <is>
+          <t>02-524</t>
+        </is>
+      </c>
+      <c r="I770" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thewinehouse.pl</t>
+        </is>
+      </c>
+      <c r="J770" s="2" t="inlineStr"/>
+      <c r="K770" s="2" t="inlineStr"/>
+      <c r="L770" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M770" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N770" s="2" t="inlineStr">
+        <is>
+          <t>info@thewinehouse.pl</t>
+        </is>
+      </c>
+      <c r="O770" s="2" t="inlineStr"/>
+      <c r="P770" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q770" s="2" t="inlineStr">
+        <is>
+          <t>5342627035</t>
+        </is>
+      </c>
+      <c r="R770" s="2" t="inlineStr"/>
+      <c r="S770" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TheWineHousePoland</t>
+        </is>
+      </c>
+      <c r="T770" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/the__wine__house/</t>
+        </is>
+      </c>
+      <c r="U770" s="2" t="inlineStr"/>
+      <c r="V770" s="2" t="inlineStr"/>
+      <c r="W770" s="2" t="inlineStr"/>
+      <c r="X770" s="2" t="inlineStr"/>
+      <c r="Y770" s="2" t="inlineStr"/>
+      <c r="Z770" s="2" t="inlineStr"/>
+      <c r="AA770" s="2" t="inlineStr"/>
+    </row>
+    <row r="771">
+      <c r="A771" s="2" t="inlineStr">
+        <is>
+          <t>Wine &amp; Style Franck Encina</t>
+        </is>
+      </c>
+      <c r="B771" s="2" t="inlineStr">
+        <is>
+          <t>Wine &amp; Style Franck Encina</t>
+        </is>
+      </c>
+      <c r="C771" s="2" t="inlineStr">
+        <is>
+          <t>121822</t>
+        </is>
+      </c>
+      <c r="D771" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E771" s="2" t="inlineStr">
+        <is>
+          <t>Warszawa</t>
+        </is>
+      </c>
+      <c r="F771" s="2" t="inlineStr">
+        <is>
+          <t>Mazowieckie</t>
+        </is>
+      </c>
+      <c r="G771" s="2" t="inlineStr">
+        <is>
+          <t>95 Łopuszańska</t>
+        </is>
+      </c>
+      <c r="H771" s="2" t="inlineStr">
+        <is>
+          <t>02-457</t>
+        </is>
+      </c>
+      <c r="I771" s="2" t="inlineStr">
+        <is>
+          <t>https://wineandstyle.pl</t>
+        </is>
+      </c>
+      <c r="J771" s="2" t="inlineStr"/>
+      <c r="K771" s="2" t="inlineStr"/>
+      <c r="L771" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M771" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N771" s="2" t="inlineStr">
+        <is>
+          <t>kontakt@wineandstyle.pl</t>
+        </is>
+      </c>
+      <c r="O771" s="2" t="inlineStr"/>
+      <c r="P771" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q771" s="2" t="inlineStr">
+        <is>
+          <t>5222880866</t>
+        </is>
+      </c>
+      <c r="R771" s="2" t="inlineStr"/>
+      <c r="S771" s="2" t="inlineStr"/>
+      <c r="T771" s="2" t="inlineStr"/>
+      <c r="U771" s="2" t="inlineStr"/>
+      <c r="V771" s="2" t="inlineStr"/>
+      <c r="W771" s="2" t="inlineStr">
+        <is>
+          <t>Frank Encina</t>
+        </is>
+      </c>
+      <c r="X771" s="2" t="inlineStr">
+        <is>
+          <t>Wine Importer &amp; Distributor</t>
+        </is>
+      </c>
+      <c r="Y771" s="2" t="inlineStr"/>
+      <c r="Z771" s="2" t="inlineStr"/>
+      <c r="AA771" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/frank-encina-97ab9731/</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="2" t="inlineStr">
+        <is>
+          <t>Winnice Francji Sp Z O O</t>
+        </is>
+      </c>
+      <c r="B772" s="2" t="inlineStr">
+        <is>
+          <t>Winnice Francji Sp Z O O</t>
+        </is>
+      </c>
+      <c r="C772" s="2" t="inlineStr">
+        <is>
+          <t>54933</t>
+        </is>
+      </c>
+      <c r="D772" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E772" s="2" t="inlineStr">
+        <is>
+          <t>Kraków</t>
+        </is>
+      </c>
+      <c r="F772" s="2" t="inlineStr">
+        <is>
+          <t>Małopolskie</t>
+        </is>
+      </c>
+      <c r="G772" s="2" t="inlineStr">
+        <is>
+          <t>17 Tadeusza Romanowicza</t>
+        </is>
+      </c>
+      <c r="H772" s="2" t="inlineStr">
+        <is>
+          <t>30-702</t>
+        </is>
+      </c>
+      <c r="I772" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winnicefrancji.pl</t>
+        </is>
+      </c>
+      <c r="J772" s="2" t="inlineStr"/>
+      <c r="K772" s="2" t="inlineStr"/>
+      <c r="L772" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M772" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N772" s="2" t="inlineStr">
+        <is>
+          <t>epariselle@winnicefrancji.pl</t>
+        </is>
+      </c>
+      <c r="O772" s="2" t="inlineStr"/>
+      <c r="P772" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q772" s="2" t="inlineStr">
+        <is>
+          <t>7251002158</t>
+        </is>
+      </c>
+      <c r="R772" s="2" t="inlineStr"/>
+      <c r="S772" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WinaZFrancji</t>
+        </is>
+      </c>
+      <c r="T772" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winnice_francji/</t>
+        </is>
+      </c>
+      <c r="U772" s="2" t="inlineStr"/>
+      <c r="V772" s="2" t="inlineStr"/>
+      <c r="W772" s="2" t="inlineStr">
+        <is>
+          <t>Beata Pieczko</t>
+        </is>
+      </c>
+      <c r="X772" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y772" s="2" t="inlineStr"/>
+      <c r="Z772" s="2" t="inlineStr"/>
+      <c r="AA772" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/beata-pieczko-1135086/</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="2" t="inlineStr">
+        <is>
+          <t>Lewiatan Holding S A</t>
+        </is>
+      </c>
+      <c r="B773" s="2" t="inlineStr">
+        <is>
+          <t>Lewiatan Holding S A</t>
+        </is>
+      </c>
+      <c r="C773" s="2" t="inlineStr">
+        <is>
+          <t>78224</t>
+        </is>
+      </c>
+      <c r="D773" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E773" s="2" t="inlineStr">
+        <is>
+          <t>Włocławek</t>
+        </is>
+      </c>
+      <c r="F773" s="2" t="inlineStr">
+        <is>
+          <t>Województwo kujawsko-pomorskie, Powiat Włocławek</t>
+        </is>
+      </c>
+      <c r="G773" s="2" t="inlineStr">
+        <is>
+          <t>10 Jana Kilińskiego</t>
+        </is>
+      </c>
+      <c r="H773" s="2" t="inlineStr">
+        <is>
+          <t>87-800</t>
+        </is>
+      </c>
+      <c r="I773" s="2" t="inlineStr">
+        <is>
+          <t>https://lewiatan.pl</t>
+        </is>
+      </c>
+      <c r="J773" s="2" t="inlineStr"/>
+      <c r="K773" s="2" t="inlineStr"/>
+      <c r="L773" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="M773" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N773" s="2" t="inlineStr">
+        <is>
+          <t>robert.rekas@lewiatan.pl</t>
+        </is>
+      </c>
+      <c r="O773" s="2" t="inlineStr">
+        <is>
+          <t>+48 54 412 78 21</t>
+        </is>
+      </c>
+      <c r="P773" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q773" s="2" t="inlineStr">
+        <is>
+          <t>6181020505</t>
+        </is>
+      </c>
+      <c r="R773" s="2" t="inlineStr"/>
+      <c r="S773" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/psh.lewiatan/</t>
+        </is>
+      </c>
+      <c r="T773" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lewiatanlubelskie/</t>
+        </is>
+      </c>
+      <c r="U773" s="2" t="inlineStr"/>
+      <c r="V773" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PSHLewiatan/f</t>
+        </is>
+      </c>
+      <c r="W773" s="2" t="inlineStr">
+        <is>
+          <t>Artur Ratajczyk</t>
+        </is>
+      </c>
+      <c r="X773" s="2" t="inlineStr">
+        <is>
+          <t>Senior Merchant</t>
+        </is>
+      </c>
+      <c r="Y773" s="2" t="inlineStr"/>
+      <c r="Z773" s="2" t="inlineStr"/>
+      <c r="AA773" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/artur-ratajczyk-23a28a217/</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="2" t="inlineStr">
+        <is>
+          <t>Lewiatan Holding S A</t>
+        </is>
+      </c>
+      <c r="B774" s="2" t="inlineStr">
+        <is>
+          <t>Lewiatan Holding S A</t>
+        </is>
+      </c>
+      <c r="C774" s="2" t="inlineStr">
+        <is>
+          <t>78224</t>
+        </is>
+      </c>
+      <c r="D774" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E774" s="2" t="inlineStr">
+        <is>
+          <t>Włocławek</t>
+        </is>
+      </c>
+      <c r="F774" s="2" t="inlineStr">
+        <is>
+          <t>Województwo kujawsko-pomorskie, Powiat Włocławek</t>
+        </is>
+      </c>
+      <c r="G774" s="2" t="inlineStr">
+        <is>
+          <t>10 Jana Kilińskiego</t>
+        </is>
+      </c>
+      <c r="H774" s="2" t="inlineStr">
+        <is>
+          <t>87-800</t>
+        </is>
+      </c>
+      <c r="I774" s="2" t="inlineStr">
+        <is>
+          <t>https://lewiatan.pl</t>
+        </is>
+      </c>
+      <c r="J774" s="2" t="inlineStr"/>
+      <c r="K774" s="2" t="inlineStr"/>
+      <c r="L774" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="M774" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N774" s="2" t="inlineStr">
+        <is>
+          <t>robert.rekas@lewiatan.pl</t>
+        </is>
+      </c>
+      <c r="O774" s="2" t="inlineStr">
+        <is>
+          <t>+48 54 412 78 21</t>
+        </is>
+      </c>
+      <c r="P774" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q774" s="2" t="inlineStr">
+        <is>
+          <t>6181020505</t>
+        </is>
+      </c>
+      <c r="R774" s="2" t="inlineStr"/>
+      <c r="S774" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/psh.lewiatan/</t>
+        </is>
+      </c>
+      <c r="T774" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lewiatanlubelskie/</t>
+        </is>
+      </c>
+      <c r="U774" s="2" t="inlineStr"/>
+      <c r="V774" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PSHLewiatan/f</t>
+        </is>
+      </c>
+      <c r="W774" s="2" t="inlineStr">
+        <is>
+          <t>Katarzyna Zaborowicz</t>
+        </is>
+      </c>
+      <c r="X774" s="2" t="inlineStr">
+        <is>
+          <t>National Category Group Management Manager</t>
+        </is>
+      </c>
+      <c r="Y774" s="2" t="inlineStr"/>
+      <c r="Z774" s="2" t="inlineStr"/>
+      <c r="AA774" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/katarzyna-zaborowicz-584bb5186/</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="2" t="inlineStr">
+        <is>
+          <t>Lewiatan Holding S A</t>
+        </is>
+      </c>
+      <c r="B775" s="2" t="inlineStr">
+        <is>
+          <t>Lewiatan Holding S A</t>
+        </is>
+      </c>
+      <c r="C775" s="2" t="inlineStr">
+        <is>
+          <t>78224</t>
+        </is>
+      </c>
+      <c r="D775" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E775" s="2" t="inlineStr">
+        <is>
+          <t>Włocławek</t>
+        </is>
+      </c>
+      <c r="F775" s="2" t="inlineStr">
+        <is>
+          <t>Województwo kujawsko-pomorskie, Powiat Włocławek</t>
+        </is>
+      </c>
+      <c r="G775" s="2" t="inlineStr">
+        <is>
+          <t>10 Jana Kilińskiego</t>
+        </is>
+      </c>
+      <c r="H775" s="2" t="inlineStr">
+        <is>
+          <t>87-800</t>
+        </is>
+      </c>
+      <c r="I775" s="2" t="inlineStr">
+        <is>
+          <t>https://lewiatan.pl</t>
+        </is>
+      </c>
+      <c r="J775" s="2" t="inlineStr"/>
+      <c r="K775" s="2" t="inlineStr"/>
+      <c r="L775" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="M775" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N775" s="2" t="inlineStr">
+        <is>
+          <t>robert.rekas@lewiatan.pl</t>
+        </is>
+      </c>
+      <c r="O775" s="2" t="inlineStr">
+        <is>
+          <t>+48 54 412 78 21</t>
+        </is>
+      </c>
+      <c r="P775" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q775" s="2" t="inlineStr">
+        <is>
+          <t>6181020505</t>
+        </is>
+      </c>
+      <c r="R775" s="2" t="inlineStr"/>
+      <c r="S775" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/psh.lewiatan/</t>
+        </is>
+      </c>
+      <c r="T775" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lewiatanlubelskie/</t>
+        </is>
+      </c>
+      <c r="U775" s="2" t="inlineStr"/>
+      <c r="V775" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PSHLewiatan/f</t>
+        </is>
+      </c>
+      <c r="W775" s="2" t="inlineStr">
+        <is>
+          <t>Robert Rękas</t>
+        </is>
+      </c>
+      <c r="X775" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y775" s="2" t="inlineStr"/>
+      <c r="Z775" s="2" t="inlineStr"/>
+      <c r="AA775" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/robert-r%C4%99kas-959b51113/</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="2" t="inlineStr">
+        <is>
+          <t>Arhelan Sp Z O O</t>
+        </is>
+      </c>
+      <c r="B776" s="2" t="inlineStr">
+        <is>
+          <t>Arhelan Sp Z O O</t>
+        </is>
+      </c>
+      <c r="C776" s="2" t="inlineStr">
+        <is>
+          <t>11229</t>
+        </is>
+      </c>
+      <c r="D776" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E776" s="2" t="inlineStr">
+        <is>
+          <t>Bielsk Podlaski</t>
+        </is>
+      </c>
+      <c r="F776" s="2" t="inlineStr">
+        <is>
+          <t>Województwo podlaskie, Powiat bielski</t>
+        </is>
+      </c>
+      <c r="G776" s="2" t="inlineStr">
+        <is>
+          <t>45 Al. Józefa Piłsudskiego</t>
+        </is>
+      </c>
+      <c r="H776" s="2" t="inlineStr">
+        <is>
+          <t>17-100</t>
+        </is>
+      </c>
+      <c r="I776" s="2" t="inlineStr">
+        <is>
+          <t>https://arhelan.pl</t>
+        </is>
+      </c>
+      <c r="J776" s="2" t="inlineStr"/>
+      <c r="K776" s="2" t="inlineStr"/>
+      <c r="L776" s="2" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="M776" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N776" s="2" t="inlineStr">
+        <is>
+          <t>agnieszka.kindziuk@arhelan.pl</t>
+        </is>
+      </c>
+      <c r="O776" s="2" t="inlineStr">
+        <is>
+          <t>+48 85 730 20 03</t>
+        </is>
+      </c>
+      <c r="P776" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q776" s="2" t="inlineStr">
+        <is>
+          <t>5430001447</t>
+        </is>
+      </c>
+      <c r="R776" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/arhelan-burzy%C5%84scy-sp-j/</t>
+        </is>
+      </c>
+      <c r="S776" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SklepyArhelan/</t>
+        </is>
+      </c>
+      <c r="T776" s="2" t="inlineStr"/>
+      <c r="U776" s="2" t="inlineStr"/>
+      <c r="V776" s="2" t="inlineStr"/>
+      <c r="W776" s="2" t="inlineStr">
+        <is>
+          <t>Agnieszka Kindziuk</t>
+        </is>
+      </c>
+      <c r="X776" s="2" t="inlineStr">
+        <is>
+          <t>Deputy Sales Director</t>
+        </is>
+      </c>
+      <c r="Y776" s="2" t="inlineStr"/>
+      <c r="Z776" s="2" t="inlineStr"/>
+      <c r="AA776" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/agnieszka-kindziuk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="2" t="inlineStr">
+        <is>
+          <t>Arhelan Sp Z O O</t>
+        </is>
+      </c>
+      <c r="B777" s="2" t="inlineStr">
+        <is>
+          <t>Arhelan Sp Z O O</t>
+        </is>
+      </c>
+      <c r="C777" s="2" t="inlineStr">
+        <is>
+          <t>11229</t>
+        </is>
+      </c>
+      <c r="D777" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E777" s="2" t="inlineStr">
+        <is>
+          <t>Bielsk Podlaski</t>
+        </is>
+      </c>
+      <c r="F777" s="2" t="inlineStr">
+        <is>
+          <t>Województwo podlaskie, Powiat bielski</t>
+        </is>
+      </c>
+      <c r="G777" s="2" t="inlineStr">
+        <is>
+          <t>45 Al. Józefa Piłsudskiego</t>
+        </is>
+      </c>
+      <c r="H777" s="2" t="inlineStr">
+        <is>
+          <t>17-100</t>
+        </is>
+      </c>
+      <c r="I777" s="2" t="inlineStr">
+        <is>
+          <t>https://arhelan.pl</t>
+        </is>
+      </c>
+      <c r="J777" s="2" t="inlineStr"/>
+      <c r="K777" s="2" t="inlineStr"/>
+      <c r="L777" s="2" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="M777" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N777" s="2" t="inlineStr">
+        <is>
+          <t>agnieszka.kindziuk@arhelan.pl</t>
+        </is>
+      </c>
+      <c r="O777" s="2" t="inlineStr">
+        <is>
+          <t>+48 85 730 20 03</t>
+        </is>
+      </c>
+      <c r="P777" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q777" s="2" t="inlineStr">
+        <is>
+          <t>5430001447</t>
+        </is>
+      </c>
+      <c r="R777" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/arhelan-burzy%C5%84scy-sp-j/</t>
+        </is>
+      </c>
+      <c r="S777" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SklepyArhelan/</t>
+        </is>
+      </c>
+      <c r="T777" s="2" t="inlineStr"/>
+      <c r="U777" s="2" t="inlineStr"/>
+      <c r="V777" s="2" t="inlineStr"/>
+      <c r="W777" s="2" t="inlineStr">
+        <is>
+          <t>Joanna Namojlik</t>
+        </is>
+      </c>
+      <c r="X777" s="2" t="inlineStr">
+        <is>
+          <t>Regional Operations Manager</t>
+        </is>
+      </c>
+      <c r="Y777" s="2" t="inlineStr"/>
+      <c r="Z777" s="2" t="inlineStr"/>
+      <c r="AA777" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/joanna-namojlik-439b16280/</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="B778" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="C778" s="2" t="inlineStr">
+        <is>
+          <t>78034</t>
+        </is>
+      </c>
+      <c r="D778" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E778" s="2" t="inlineStr">
+        <is>
+          <t>Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="F778" s="2" t="inlineStr">
+        <is>
+          <t>Województwo kujawsko-pomorskie, Powiat Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="G778" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Mokra 30</t>
+        </is>
+      </c>
+      <c r="H778" s="2" t="inlineStr">
+        <is>
+          <t>85-834</t>
+        </is>
+      </c>
+      <c r="I778" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.pl</t>
+        </is>
+      </c>
+      <c r="J778" s="2" t="inlineStr"/>
+      <c r="K778" s="2" t="inlineStr"/>
+      <c r="L778" s="2" t="inlineStr"/>
+      <c r="M778" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N778" s="2" t="inlineStr">
+        <is>
+          <t>lmucha@bidfood.pl</t>
+        </is>
+      </c>
+      <c r="O778" s="2" t="inlineStr">
+        <is>
+          <t>+48 52 360 75 01</t>
+        </is>
+      </c>
+      <c r="P778" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q778" s="2" t="inlineStr">
+        <is>
+          <t>5921987110</t>
+        </is>
+      </c>
+      <c r="R778" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/farutex/</t>
+        </is>
+      </c>
+      <c r="S778" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="T778" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="U778" s="2" t="inlineStr"/>
+      <c r="V778" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCg0GPcESE_uDY_WZJITDpUw</t>
+        </is>
+      </c>
+      <c r="W778" s="2" t="inlineStr">
+        <is>
+          <t>Łukasz Mucha</t>
+        </is>
+      </c>
+      <c r="X778" s="2" t="inlineStr">
+        <is>
+          <t>Manager of Purchasing Department</t>
+        </is>
+      </c>
+      <c r="Y778" s="2" t="inlineStr"/>
+      <c r="Z778" s="2" t="inlineStr"/>
+      <c r="AA778" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/%C5%82ukasz-mucha-972a6596</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="B779" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="C779" s="2" t="inlineStr">
+        <is>
+          <t>78034</t>
+        </is>
+      </c>
+      <c r="D779" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E779" s="2" t="inlineStr">
+        <is>
+          <t>Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="F779" s="2" t="inlineStr">
+        <is>
+          <t>Województwo kujawsko-pomorskie, Powiat Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="G779" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Mokra 30</t>
+        </is>
+      </c>
+      <c r="H779" s="2" t="inlineStr">
+        <is>
+          <t>85-834</t>
+        </is>
+      </c>
+      <c r="I779" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.pl</t>
+        </is>
+      </c>
+      <c r="J779" s="2" t="inlineStr"/>
+      <c r="K779" s="2" t="inlineStr"/>
+      <c r="L779" s="2" t="inlineStr"/>
+      <c r="M779" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N779" s="2" t="inlineStr">
+        <is>
+          <t>lmucha@bidfood.pl</t>
+        </is>
+      </c>
+      <c r="O779" s="2" t="inlineStr">
+        <is>
+          <t>+48 52 360 75 01</t>
+        </is>
+      </c>
+      <c r="P779" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q779" s="2" t="inlineStr">
+        <is>
+          <t>5921987110</t>
+        </is>
+      </c>
+      <c r="R779" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/farutex/</t>
+        </is>
+      </c>
+      <c r="S779" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="T779" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="U779" s="2" t="inlineStr"/>
+      <c r="V779" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCg0GPcESE_uDY_WZJITDpUw</t>
+        </is>
+      </c>
+      <c r="W779" s="2" t="inlineStr">
+        <is>
+          <t>Martyna Foremna-pitala</t>
+        </is>
+      </c>
+      <c r="X779" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager Brands Fine Wine</t>
+        </is>
+      </c>
+      <c r="Y779" s="2" t="inlineStr"/>
+      <c r="Z779" s="2" t="inlineStr"/>
+      <c r="AA779" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/martyna-foremna-pitala-57961684/</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="B780" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="C780" s="2" t="inlineStr">
+        <is>
+          <t>78034</t>
+        </is>
+      </c>
+      <c r="D780" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E780" s="2" t="inlineStr">
+        <is>
+          <t>Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="F780" s="2" t="inlineStr">
+        <is>
+          <t>Województwo kujawsko-pomorskie, Powiat Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="G780" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Mokra 30</t>
+        </is>
+      </c>
+      <c r="H780" s="2" t="inlineStr">
+        <is>
+          <t>85-834</t>
+        </is>
+      </c>
+      <c r="I780" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.pl</t>
+        </is>
+      </c>
+      <c r="J780" s="2" t="inlineStr"/>
+      <c r="K780" s="2" t="inlineStr"/>
+      <c r="L780" s="2" t="inlineStr"/>
+      <c r="M780" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N780" s="2" t="inlineStr">
+        <is>
+          <t>lmucha@bidfood.pl</t>
+        </is>
+      </c>
+      <c r="O780" s="2" t="inlineStr">
+        <is>
+          <t>+48 52 360 75 01</t>
+        </is>
+      </c>
+      <c r="P780" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q780" s="2" t="inlineStr">
+        <is>
+          <t>5921987110</t>
+        </is>
+      </c>
+      <c r="R780" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/farutex/</t>
+        </is>
+      </c>
+      <c r="S780" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="T780" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="U780" s="2" t="inlineStr"/>
+      <c r="V780" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCg0GPcESE_uDY_WZJITDpUw</t>
+        </is>
+      </c>
+      <c r="W780" s="2" t="inlineStr">
+        <is>
+          <t>Krzysztof Ligaj</t>
+        </is>
+      </c>
+      <c r="X780" s="2" t="inlineStr">
+        <is>
+          <t>Category Commercial Buyer</t>
+        </is>
+      </c>
+      <c r="Y780" s="2" t="inlineStr"/>
+      <c r="Z780" s="2" t="inlineStr"/>
+      <c r="AA780" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/krzysztof-ligaj-858998143/</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="B781" s="2" t="inlineStr">
+        <is>
+          <t>Farutex Sp Z O O</t>
+        </is>
+      </c>
+      <c r="C781" s="2" t="inlineStr">
+        <is>
+          <t>78034</t>
+        </is>
+      </c>
+      <c r="D781" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E781" s="2" t="inlineStr">
+        <is>
+          <t>Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="F781" s="2" t="inlineStr">
+        <is>
+          <t>Województwo kujawsko-pomorskie, Powiat Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="G781" s="2" t="inlineStr">
+        <is>
+          <t>Ul. Mokra 30</t>
+        </is>
+      </c>
+      <c r="H781" s="2" t="inlineStr">
+        <is>
+          <t>85-834</t>
+        </is>
+      </c>
+      <c r="I781" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.pl</t>
+        </is>
+      </c>
+      <c r="J781" s="2" t="inlineStr"/>
+      <c r="K781" s="2" t="inlineStr"/>
+      <c r="L781" s="2" t="inlineStr"/>
+      <c r="M781" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N781" s="2" t="inlineStr">
+        <is>
+          <t>lmucha@bidfood.pl</t>
+        </is>
+      </c>
+      <c r="O781" s="2" t="inlineStr">
+        <is>
+          <t>+48 52 360 75 01</t>
+        </is>
+      </c>
+      <c r="P781" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q781" s="2" t="inlineStr">
+        <is>
+          <t>5921987110</t>
+        </is>
+      </c>
+      <c r="R781" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/farutex/</t>
+        </is>
+      </c>
+      <c r="S781" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="T781" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfoodfarutex</t>
+        </is>
+      </c>
+      <c r="U781" s="2" t="inlineStr"/>
+      <c r="V781" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCg0GPcESE_uDY_WZJITDpUw</t>
+        </is>
+      </c>
+      <c r="W781" s="2" t="inlineStr">
+        <is>
+          <t>Magdalena Kwiecień</t>
+        </is>
+      </c>
+      <c r="X781" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Specialist</t>
+        </is>
+      </c>
+      <c r="Y781" s="2" t="inlineStr"/>
+      <c r="Z781" s="2" t="inlineStr"/>
+      <c r="AA781" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/magdalena-kwiecie%c5%84-0906b5214/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Poland.xlsx
+++ b/BWI/bestwine_output/bestwine_Poland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA781"/>
+  <dimension ref="A1:AA787"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -82488,6 +82488,652 @@
         </is>
       </c>
     </row>
+    <row r="782">
+      <c r="A782" s="2" t="inlineStr">
+        <is>
+          <t>Phu łacisz</t>
+        </is>
+      </c>
+      <c r="B782" s="2" t="inlineStr">
+        <is>
+          <t>Phu łacisz</t>
+        </is>
+      </c>
+      <c r="C782" s="2" t="inlineStr">
+        <is>
+          <t>55163</t>
+        </is>
+      </c>
+      <c r="D782" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E782" s="2" t="inlineStr">
+        <is>
+          <t>Radomsko</t>
+        </is>
+      </c>
+      <c r="F782" s="2" t="inlineStr">
+        <is>
+          <t>Województwo łódzkie, Powiat radomszczański</t>
+        </is>
+      </c>
+      <c r="G782" s="2" t="inlineStr">
+        <is>
+          <t>164 Krasickiego</t>
+        </is>
+      </c>
+      <c r="H782" s="2" t="inlineStr">
+        <is>
+          <t>97-500</t>
+        </is>
+      </c>
+      <c r="I782" s="2" t="inlineStr">
+        <is>
+          <t>http://phulacisz.pl</t>
+        </is>
+      </c>
+      <c r="J782" s="2" t="inlineStr"/>
+      <c r="K782" s="2" t="inlineStr"/>
+      <c r="L782" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M782" s="2" t="inlineStr"/>
+      <c r="N782" s="2" t="inlineStr">
+        <is>
+          <t>phu.lacisz.radomsko@onet.pl</t>
+        </is>
+      </c>
+      <c r="O782" s="2" t="inlineStr"/>
+      <c r="P782" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q782" s="2" t="inlineStr">
+        <is>
+          <t>7720102790</t>
+        </is>
+      </c>
+      <c r="R782" s="2" t="inlineStr"/>
+      <c r="S782" s="2" t="inlineStr"/>
+      <c r="T782" s="2" t="inlineStr"/>
+      <c r="U782" s="2" t="inlineStr"/>
+      <c r="V782" s="2" t="inlineStr"/>
+      <c r="W782" s="2" t="inlineStr">
+        <is>
+          <t>Tadeusz Łacisz</t>
+        </is>
+      </c>
+      <c r="X782" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y782" s="2" t="inlineStr"/>
+      <c r="Z782" s="2" t="inlineStr"/>
+      <c r="AA782" s="2" t="inlineStr"/>
+    </row>
+    <row r="783">
+      <c r="A783" s="2" t="inlineStr">
+        <is>
+          <t>Dom Wina Sp. Z O.o.</t>
+        </is>
+      </c>
+      <c r="B783" s="2" t="inlineStr">
+        <is>
+          <t>Dom Wina Sp. Z O.o.</t>
+        </is>
+      </c>
+      <c r="C783" s="2" t="inlineStr">
+        <is>
+          <t>11076</t>
+        </is>
+      </c>
+      <c r="D783" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E783" s="2" t="inlineStr">
+        <is>
+          <t>Kraków</t>
+        </is>
+      </c>
+      <c r="F783" s="2" t="inlineStr">
+        <is>
+          <t>Małopolskie</t>
+        </is>
+      </c>
+      <c r="G783" s="2" t="inlineStr">
+        <is>
+          <t>255 Balicka</t>
+        </is>
+      </c>
+      <c r="H783" s="2" t="inlineStr">
+        <is>
+          <t>30-198</t>
+        </is>
+      </c>
+      <c r="I783" s="2" t="inlineStr">
+        <is>
+          <t>https://domwina.pl</t>
+        </is>
+      </c>
+      <c r="J783" s="2" t="inlineStr"/>
+      <c r="K783" s="2" t="inlineStr"/>
+      <c r="L783" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M783" s="2" t="inlineStr"/>
+      <c r="N783" s="2" t="inlineStr">
+        <is>
+          <t>info@domwina.pl</t>
+        </is>
+      </c>
+      <c r="O783" s="2" t="inlineStr">
+        <is>
+          <t>+48 12 638 13 80</t>
+        </is>
+      </c>
+      <c r="P783" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q783" s="2" t="inlineStr">
+        <is>
+          <t>6771697284</t>
+        </is>
+      </c>
+      <c r="R783" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dom-wina-sp.-z-o.o./</t>
+        </is>
+      </c>
+      <c r="S783" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KlubDomuWina/</t>
+        </is>
+      </c>
+      <c r="T783" s="2" t="inlineStr"/>
+      <c r="U783" s="2" t="inlineStr"/>
+      <c r="V783" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/DworSierakowPl</t>
+        </is>
+      </c>
+      <c r="W783" s="2" t="inlineStr">
+        <is>
+          <t>Michał Stępień</t>
+        </is>
+      </c>
+      <c r="X783" s="2" t="inlineStr">
+        <is>
+          <t>Sommelier</t>
+        </is>
+      </c>
+      <c r="Y783" s="2" t="inlineStr"/>
+      <c r="Z783" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA783" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/micha%C5%82-st%C4%99pie%C5%84-2058b95b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="2" t="inlineStr">
+        <is>
+          <t>Dom Wina Sp. Z O.o.</t>
+        </is>
+      </c>
+      <c r="B784" s="2" t="inlineStr">
+        <is>
+          <t>Dom Wina Sp. Z O.o.</t>
+        </is>
+      </c>
+      <c r="C784" s="2" t="inlineStr">
+        <is>
+          <t>11076</t>
+        </is>
+      </c>
+      <c r="D784" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E784" s="2" t="inlineStr">
+        <is>
+          <t>Kraków</t>
+        </is>
+      </c>
+      <c r="F784" s="2" t="inlineStr">
+        <is>
+          <t>Małopolskie</t>
+        </is>
+      </c>
+      <c r="G784" s="2" t="inlineStr">
+        <is>
+          <t>255 Balicka</t>
+        </is>
+      </c>
+      <c r="H784" s="2" t="inlineStr">
+        <is>
+          <t>30-198</t>
+        </is>
+      </c>
+      <c r="I784" s="2" t="inlineStr">
+        <is>
+          <t>https://domwina.pl</t>
+        </is>
+      </c>
+      <c r="J784" s="2" t="inlineStr"/>
+      <c r="K784" s="2" t="inlineStr"/>
+      <c r="L784" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M784" s="2" t="inlineStr"/>
+      <c r="N784" s="2" t="inlineStr">
+        <is>
+          <t>info@domwina.pl</t>
+        </is>
+      </c>
+      <c r="O784" s="2" t="inlineStr">
+        <is>
+          <t>+48 12 638 13 80</t>
+        </is>
+      </c>
+      <c r="P784" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q784" s="2" t="inlineStr">
+        <is>
+          <t>6771697284</t>
+        </is>
+      </c>
+      <c r="R784" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dom-wina-sp.-z-o.o./</t>
+        </is>
+      </c>
+      <c r="S784" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KlubDomuWina/</t>
+        </is>
+      </c>
+      <c r="T784" s="2" t="inlineStr"/>
+      <c r="U784" s="2" t="inlineStr"/>
+      <c r="V784" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/DworSierakowPl</t>
+        </is>
+      </c>
+      <c r="W784" s="2" t="inlineStr">
+        <is>
+          <t>Katarzyna Kiełb</t>
+        </is>
+      </c>
+      <c r="X784" s="2" t="inlineStr">
+        <is>
+          <t>Assistant To The Vice President Of The Board</t>
+        </is>
+      </c>
+      <c r="Y784" s="2" t="inlineStr"/>
+      <c r="Z784" s="2" t="inlineStr"/>
+      <c r="AA784" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/katarzyna-kie%c5%82b-a443648/</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="2" t="inlineStr">
+        <is>
+          <t>Dom Wina Sp. Z O.o.</t>
+        </is>
+      </c>
+      <c r="B785" s="2" t="inlineStr">
+        <is>
+          <t>Dom Wina Sp. Z O.o.</t>
+        </is>
+      </c>
+      <c r="C785" s="2" t="inlineStr">
+        <is>
+          <t>11076</t>
+        </is>
+      </c>
+      <c r="D785" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E785" s="2" t="inlineStr">
+        <is>
+          <t>Kraków</t>
+        </is>
+      </c>
+      <c r="F785" s="2" t="inlineStr">
+        <is>
+          <t>Małopolskie</t>
+        </is>
+      </c>
+      <c r="G785" s="2" t="inlineStr">
+        <is>
+          <t>255 Balicka</t>
+        </is>
+      </c>
+      <c r="H785" s="2" t="inlineStr">
+        <is>
+          <t>30-198</t>
+        </is>
+      </c>
+      <c r="I785" s="2" t="inlineStr">
+        <is>
+          <t>https://domwina.pl</t>
+        </is>
+      </c>
+      <c r="J785" s="2" t="inlineStr"/>
+      <c r="K785" s="2" t="inlineStr"/>
+      <c r="L785" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M785" s="2" t="inlineStr"/>
+      <c r="N785" s="2" t="inlineStr">
+        <is>
+          <t>info@domwina.pl</t>
+        </is>
+      </c>
+      <c r="O785" s="2" t="inlineStr">
+        <is>
+          <t>+48 12 638 13 80</t>
+        </is>
+      </c>
+      <c r="P785" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q785" s="2" t="inlineStr">
+        <is>
+          <t>6771697284</t>
+        </is>
+      </c>
+      <c r="R785" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dom-wina-sp.-z-o.o./</t>
+        </is>
+      </c>
+      <c r="S785" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KlubDomuWina/</t>
+        </is>
+      </c>
+      <c r="T785" s="2" t="inlineStr"/>
+      <c r="U785" s="2" t="inlineStr"/>
+      <c r="V785" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/DworSierakowPl</t>
+        </is>
+      </c>
+      <c r="W785" s="2" t="inlineStr">
+        <is>
+          <t>Kacper Witek</t>
+        </is>
+      </c>
+      <c r="X785" s="2" t="inlineStr">
+        <is>
+          <t>Key Account Manager</t>
+        </is>
+      </c>
+      <c r="Y785" s="2" t="inlineStr"/>
+      <c r="Z785" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA785" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/kacper-witek-132228315/</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="2" t="inlineStr">
+        <is>
+          <t>Dom Wina Sp. Z O.o.</t>
+        </is>
+      </c>
+      <c r="B786" s="2" t="inlineStr">
+        <is>
+          <t>Dom Wina Sp. Z O.o.</t>
+        </is>
+      </c>
+      <c r="C786" s="2" t="inlineStr">
+        <is>
+          <t>11076</t>
+        </is>
+      </c>
+      <c r="D786" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E786" s="2" t="inlineStr">
+        <is>
+          <t>Kraków</t>
+        </is>
+      </c>
+      <c r="F786" s="2" t="inlineStr">
+        <is>
+          <t>Małopolskie</t>
+        </is>
+      </c>
+      <c r="G786" s="2" t="inlineStr">
+        <is>
+          <t>255 Balicka</t>
+        </is>
+      </c>
+      <c r="H786" s="2" t="inlineStr">
+        <is>
+          <t>30-198</t>
+        </is>
+      </c>
+      <c r="I786" s="2" t="inlineStr">
+        <is>
+          <t>https://domwina.pl</t>
+        </is>
+      </c>
+      <c r="J786" s="2" t="inlineStr"/>
+      <c r="K786" s="2" t="inlineStr"/>
+      <c r="L786" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M786" s="2" t="inlineStr"/>
+      <c r="N786" s="2" t="inlineStr">
+        <is>
+          <t>info@domwina.pl</t>
+        </is>
+      </c>
+      <c r="O786" s="2" t="inlineStr">
+        <is>
+          <t>+48 12 638 13 80</t>
+        </is>
+      </c>
+      <c r="P786" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q786" s="2" t="inlineStr">
+        <is>
+          <t>6771697284</t>
+        </is>
+      </c>
+      <c r="R786" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dom-wina-sp.-z-o.o./</t>
+        </is>
+      </c>
+      <c r="S786" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KlubDomuWina/</t>
+        </is>
+      </c>
+      <c r="T786" s="2" t="inlineStr"/>
+      <c r="U786" s="2" t="inlineStr"/>
+      <c r="V786" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/DworSierakowPl</t>
+        </is>
+      </c>
+      <c r="W786" s="2" t="inlineStr">
+        <is>
+          <t>Artur Boruta</t>
+        </is>
+      </c>
+      <c r="X786" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y786" s="2" t="inlineStr"/>
+      <c r="Z786" s="2" t="inlineStr"/>
+      <c r="AA786" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/artur-boruta-1a643a13/</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="2" t="inlineStr">
+        <is>
+          <t>Dom Wina Sp. Z O.o.</t>
+        </is>
+      </c>
+      <c r="B787" s="2" t="inlineStr">
+        <is>
+          <t>Dom Wina Sp. Z O.o.</t>
+        </is>
+      </c>
+      <c r="C787" s="2" t="inlineStr">
+        <is>
+          <t>11076</t>
+        </is>
+      </c>
+      <c r="D787" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E787" s="2" t="inlineStr">
+        <is>
+          <t>Kraków</t>
+        </is>
+      </c>
+      <c r="F787" s="2" t="inlineStr">
+        <is>
+          <t>Małopolskie</t>
+        </is>
+      </c>
+      <c r="G787" s="2" t="inlineStr">
+        <is>
+          <t>255 Balicka</t>
+        </is>
+      </c>
+      <c r="H787" s="2" t="inlineStr">
+        <is>
+          <t>30-198</t>
+        </is>
+      </c>
+      <c r="I787" s="2" t="inlineStr">
+        <is>
+          <t>https://domwina.pl</t>
+        </is>
+      </c>
+      <c r="J787" s="2" t="inlineStr"/>
+      <c r="K787" s="2" t="inlineStr"/>
+      <c r="L787" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M787" s="2" t="inlineStr"/>
+      <c r="N787" s="2" t="inlineStr">
+        <is>
+          <t>info@domwina.pl</t>
+        </is>
+      </c>
+      <c r="O787" s="2" t="inlineStr">
+        <is>
+          <t>+48 12 638 13 80</t>
+        </is>
+      </c>
+      <c r="P787" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q787" s="2" t="inlineStr">
+        <is>
+          <t>6771697284</t>
+        </is>
+      </c>
+      <c r="R787" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dom-wina-sp.-z-o.o./</t>
+        </is>
+      </c>
+      <c r="S787" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KlubDomuWina/</t>
+        </is>
+      </c>
+      <c r="T787" s="2" t="inlineStr"/>
+      <c r="U787" s="2" t="inlineStr"/>
+      <c r="V787" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/DworSierakowPl</t>
+        </is>
+      </c>
+      <c r="W787" s="2" t="inlineStr">
+        <is>
+          <t>Lech Andrzejewski</t>
+        </is>
+      </c>
+      <c r="X787" s="2" t="inlineStr">
+        <is>
+          <t>Sales Representative, Wine Advisor</t>
+        </is>
+      </c>
+      <c r="Y787" s="2" t="inlineStr"/>
+      <c r="Z787" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA787" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/lech-andrzejewski/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Poland.xlsx
+++ b/BWI/bestwine_output/bestwine_Poland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA787"/>
+  <dimension ref="A1:AA797"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -83134,6 +83134,1088 @@
         </is>
       </c>
     </row>
+    <row r="788">
+      <c r="A788" s="2" t="inlineStr">
+        <is>
+          <t>Auchan Polska Sp. Z.o.o.</t>
+        </is>
+      </c>
+      <c r="B788" s="2" t="inlineStr">
+        <is>
+          <t>Auchan Polska Sp. Z.o.o.</t>
+        </is>
+      </c>
+      <c r="C788" s="2" t="inlineStr">
+        <is>
+          <t>33347</t>
+        </is>
+      </c>
+      <c r="D788" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E788" s="2" t="inlineStr">
+        <is>
+          <t>Piaseczno</t>
+        </is>
+      </c>
+      <c r="F788" s="2" t="inlineStr">
+        <is>
+          <t>Województwo mazowieckie, Powiat piaseczyński</t>
+        </is>
+      </c>
+      <c r="G788" s="2" t="inlineStr">
+        <is>
+          <t>46 Puławska</t>
+        </is>
+      </c>
+      <c r="H788" s="2" t="inlineStr">
+        <is>
+          <t>05-500</t>
+        </is>
+      </c>
+      <c r="I788" s="2" t="inlineStr">
+        <is>
+          <t>https://www.auchan.pl, https://zakupy.auchan.pl</t>
+        </is>
+      </c>
+      <c r="J788" s="2" t="inlineStr"/>
+      <c r="K788" s="2" t="inlineStr"/>
+      <c r="L788" s="2" t="inlineStr">
+        <is>
+          <t>17381</t>
+        </is>
+      </c>
+      <c r="M788" s="2" t="inlineStr"/>
+      <c r="N788" s="2" t="inlineStr">
+        <is>
+          <t>kontakt@auchan.pl</t>
+        </is>
+      </c>
+      <c r="O788" s="2" t="inlineStr">
+        <is>
+          <t>+48 22 444 02 22</t>
+        </is>
+      </c>
+      <c r="P788" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q788" s="2" t="inlineStr">
+        <is>
+          <t>5260309174</t>
+        </is>
+      </c>
+      <c r="R788" s="2" t="inlineStr"/>
+      <c r="S788" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/auchan-219510118687321/</t>
+        </is>
+      </c>
+      <c r="T788" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/auchan_polska/</t>
+        </is>
+      </c>
+      <c r="U788" s="2" t="inlineStr"/>
+      <c r="V788" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCwhVHql6PDT6KZg8Iphq4YA</t>
+        </is>
+      </c>
+      <c r="W788" s="2" t="inlineStr">
+        <is>
+          <t>Artur Bienduga</t>
+        </is>
+      </c>
+      <c r="X788" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y788" s="2" t="inlineStr"/>
+      <c r="Z788" s="2" t="inlineStr"/>
+      <c r="AA788" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/artur-bienduga-671b3ba0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="2" t="inlineStr">
+        <is>
+          <t>Auchan Polska Sp. Z.o.o.</t>
+        </is>
+      </c>
+      <c r="B789" s="2" t="inlineStr">
+        <is>
+          <t>Auchan Polska Sp. Z.o.o.</t>
+        </is>
+      </c>
+      <c r="C789" s="2" t="inlineStr">
+        <is>
+          <t>33347</t>
+        </is>
+      </c>
+      <c r="D789" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E789" s="2" t="inlineStr">
+        <is>
+          <t>Piaseczno</t>
+        </is>
+      </c>
+      <c r="F789" s="2" t="inlineStr">
+        <is>
+          <t>Województwo mazowieckie, Powiat piaseczyński</t>
+        </is>
+      </c>
+      <c r="G789" s="2" t="inlineStr">
+        <is>
+          <t>46 Puławska</t>
+        </is>
+      </c>
+      <c r="H789" s="2" t="inlineStr">
+        <is>
+          <t>05-500</t>
+        </is>
+      </c>
+      <c r="I789" s="2" t="inlineStr">
+        <is>
+          <t>https://www.auchan.pl, https://zakupy.auchan.pl</t>
+        </is>
+      </c>
+      <c r="J789" s="2" t="inlineStr"/>
+      <c r="K789" s="2" t="inlineStr"/>
+      <c r="L789" s="2" t="inlineStr">
+        <is>
+          <t>17381</t>
+        </is>
+      </c>
+      <c r="M789" s="2" t="inlineStr"/>
+      <c r="N789" s="2" t="inlineStr">
+        <is>
+          <t>kontakt@auchan.pl</t>
+        </is>
+      </c>
+      <c r="O789" s="2" t="inlineStr">
+        <is>
+          <t>+48 22 444 02 22</t>
+        </is>
+      </c>
+      <c r="P789" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q789" s="2" t="inlineStr">
+        <is>
+          <t>5260309174</t>
+        </is>
+      </c>
+      <c r="R789" s="2" t="inlineStr"/>
+      <c r="S789" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/auchan-219510118687321/</t>
+        </is>
+      </c>
+      <c r="T789" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/auchan_polska/</t>
+        </is>
+      </c>
+      <c r="U789" s="2" t="inlineStr"/>
+      <c r="V789" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCwhVHql6PDT6KZg8Iphq4YA</t>
+        </is>
+      </c>
+      <c r="W789" s="2" t="inlineStr">
+        <is>
+          <t>Monika Leniak</t>
+        </is>
+      </c>
+      <c r="X789" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y789" s="2" t="inlineStr"/>
+      <c r="Z789" s="2" t="inlineStr"/>
+      <c r="AA789" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/monika-leniak-6a362514a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="2" t="inlineStr">
+        <is>
+          <t>Auchan Polska Sp. Z.o.o.</t>
+        </is>
+      </c>
+      <c r="B790" s="2" t="inlineStr">
+        <is>
+          <t>Auchan Polska Sp. Z.o.o.</t>
+        </is>
+      </c>
+      <c r="C790" s="2" t="inlineStr">
+        <is>
+          <t>33347</t>
+        </is>
+      </c>
+      <c r="D790" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E790" s="2" t="inlineStr">
+        <is>
+          <t>Piaseczno</t>
+        </is>
+      </c>
+      <c r="F790" s="2" t="inlineStr">
+        <is>
+          <t>Województwo mazowieckie, Powiat piaseczyński</t>
+        </is>
+      </c>
+      <c r="G790" s="2" t="inlineStr">
+        <is>
+          <t>46 Puławska</t>
+        </is>
+      </c>
+      <c r="H790" s="2" t="inlineStr">
+        <is>
+          <t>05-500</t>
+        </is>
+      </c>
+      <c r="I790" s="2" t="inlineStr">
+        <is>
+          <t>https://www.auchan.pl, https://zakupy.auchan.pl</t>
+        </is>
+      </c>
+      <c r="J790" s="2" t="inlineStr"/>
+      <c r="K790" s="2" t="inlineStr"/>
+      <c r="L790" s="2" t="inlineStr">
+        <is>
+          <t>17381</t>
+        </is>
+      </c>
+      <c r="M790" s="2" t="inlineStr"/>
+      <c r="N790" s="2" t="inlineStr">
+        <is>
+          <t>kontakt@auchan.pl</t>
+        </is>
+      </c>
+      <c r="O790" s="2" t="inlineStr">
+        <is>
+          <t>+48 22 444 02 22</t>
+        </is>
+      </c>
+      <c r="P790" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q790" s="2" t="inlineStr">
+        <is>
+          <t>5260309174</t>
+        </is>
+      </c>
+      <c r="R790" s="2" t="inlineStr"/>
+      <c r="S790" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/auchan-219510118687321/</t>
+        </is>
+      </c>
+      <c r="T790" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/auchan_polska/</t>
+        </is>
+      </c>
+      <c r="U790" s="2" t="inlineStr"/>
+      <c r="V790" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCwhVHql6PDT6KZg8Iphq4YA</t>
+        </is>
+      </c>
+      <c r="W790" s="2" t="inlineStr">
+        <is>
+          <t>Nicolas Idkowiak</t>
+        </is>
+      </c>
+      <c r="X790" s="2" t="inlineStr">
+        <is>
+          <t>Beer Distributor, Private Label Brands</t>
+        </is>
+      </c>
+      <c r="Y790" s="2" t="inlineStr"/>
+      <c r="Z790" s="2" t="inlineStr"/>
+      <c r="AA790" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nicolas-idkowiak-a0630a78/</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="2" t="inlineStr">
+        <is>
+          <t>Auchan Polska Sp. Z.o.o.</t>
+        </is>
+      </c>
+      <c r="B791" s="2" t="inlineStr">
+        <is>
+          <t>Auchan Polska Sp. Z.o.o.</t>
+        </is>
+      </c>
+      <c r="C791" s="2" t="inlineStr">
+        <is>
+          <t>33347</t>
+        </is>
+      </c>
+      <c r="D791" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E791" s="2" t="inlineStr">
+        <is>
+          <t>Piaseczno</t>
+        </is>
+      </c>
+      <c r="F791" s="2" t="inlineStr">
+        <is>
+          <t>Województwo mazowieckie, Powiat piaseczyński</t>
+        </is>
+      </c>
+      <c r="G791" s="2" t="inlineStr">
+        <is>
+          <t>46 Puławska</t>
+        </is>
+      </c>
+      <c r="H791" s="2" t="inlineStr">
+        <is>
+          <t>05-500</t>
+        </is>
+      </c>
+      <c r="I791" s="2" t="inlineStr">
+        <is>
+          <t>https://www.auchan.pl, https://zakupy.auchan.pl</t>
+        </is>
+      </c>
+      <c r="J791" s="2" t="inlineStr"/>
+      <c r="K791" s="2" t="inlineStr"/>
+      <c r="L791" s="2" t="inlineStr">
+        <is>
+          <t>17381</t>
+        </is>
+      </c>
+      <c r="M791" s="2" t="inlineStr"/>
+      <c r="N791" s="2" t="inlineStr">
+        <is>
+          <t>kontakt@auchan.pl</t>
+        </is>
+      </c>
+      <c r="O791" s="2" t="inlineStr">
+        <is>
+          <t>+48 22 444 02 22</t>
+        </is>
+      </c>
+      <c r="P791" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q791" s="2" t="inlineStr">
+        <is>
+          <t>5260309174</t>
+        </is>
+      </c>
+      <c r="R791" s="2" t="inlineStr"/>
+      <c r="S791" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/auchan-219510118687321/</t>
+        </is>
+      </c>
+      <c r="T791" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/auchan_polska/</t>
+        </is>
+      </c>
+      <c r="U791" s="2" t="inlineStr"/>
+      <c r="V791" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCwhVHql6PDT6KZg8Iphq4YA</t>
+        </is>
+      </c>
+      <c r="W791" s="2" t="inlineStr">
+        <is>
+          <t>Jacek Płoński</t>
+        </is>
+      </c>
+      <c r="X791" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y791" s="2" t="inlineStr"/>
+      <c r="Z791" s="2" t="inlineStr"/>
+      <c r="AA791" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jacek-p%C5%82o%C5%84ski-95990b120/</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="2" t="inlineStr">
+        <is>
+          <t>Phu łacisz</t>
+        </is>
+      </c>
+      <c r="B792" s="2" t="inlineStr">
+        <is>
+          <t>Phu łacisz</t>
+        </is>
+      </c>
+      <c r="C792" s="2" t="inlineStr">
+        <is>
+          <t>55163</t>
+        </is>
+      </c>
+      <c r="D792" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E792" s="2" t="inlineStr">
+        <is>
+          <t>Radomsko</t>
+        </is>
+      </c>
+      <c r="F792" s="2" t="inlineStr">
+        <is>
+          <t>Województwo łódzkie, Powiat radomszczański</t>
+        </is>
+      </c>
+      <c r="G792" s="2" t="inlineStr">
+        <is>
+          <t>164 Krasickiego</t>
+        </is>
+      </c>
+      <c r="H792" s="2" t="inlineStr">
+        <is>
+          <t>97-500</t>
+        </is>
+      </c>
+      <c r="I792" s="2" t="inlineStr">
+        <is>
+          <t>http://phulacisz.pl</t>
+        </is>
+      </c>
+      <c r="J792" s="2" t="inlineStr"/>
+      <c r="K792" s="2" t="inlineStr"/>
+      <c r="L792" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M792" s="2" t="inlineStr"/>
+      <c r="N792" s="2" t="inlineStr">
+        <is>
+          <t>phu.lacisz.radomsko@onet.pl</t>
+        </is>
+      </c>
+      <c r="O792" s="2" t="inlineStr"/>
+      <c r="P792" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q792" s="2" t="inlineStr">
+        <is>
+          <t>7720102790</t>
+        </is>
+      </c>
+      <c r="R792" s="2" t="inlineStr"/>
+      <c r="S792" s="2" t="inlineStr"/>
+      <c r="T792" s="2" t="inlineStr"/>
+      <c r="U792" s="2" t="inlineStr"/>
+      <c r="V792" s="2" t="inlineStr"/>
+      <c r="W792" s="2" t="inlineStr">
+        <is>
+          <t>Tadeusz Łacisz</t>
+        </is>
+      </c>
+      <c r="X792" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y792" s="2" t="inlineStr"/>
+      <c r="Z792" s="2" t="inlineStr"/>
+      <c r="AA792" s="2" t="inlineStr"/>
+    </row>
+    <row r="793">
+      <c r="A793" s="2" t="inlineStr">
+        <is>
+          <t>Dom Wina Sp. Z O.o.</t>
+        </is>
+      </c>
+      <c r="B793" s="2" t="inlineStr">
+        <is>
+          <t>Dom Wina Sp. Z O.o.</t>
+        </is>
+      </c>
+      <c r="C793" s="2" t="inlineStr">
+        <is>
+          <t>11076</t>
+        </is>
+      </c>
+      <c r="D793" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E793" s="2" t="inlineStr">
+        <is>
+          <t>Kraków</t>
+        </is>
+      </c>
+      <c r="F793" s="2" t="inlineStr">
+        <is>
+          <t>Małopolskie</t>
+        </is>
+      </c>
+      <c r="G793" s="2" t="inlineStr">
+        <is>
+          <t>255 Balicka</t>
+        </is>
+      </c>
+      <c r="H793" s="2" t="inlineStr">
+        <is>
+          <t>30-198</t>
+        </is>
+      </c>
+      <c r="I793" s="2" t="inlineStr">
+        <is>
+          <t>https://domwina.pl</t>
+        </is>
+      </c>
+      <c r="J793" s="2" t="inlineStr"/>
+      <c r="K793" s="2" t="inlineStr"/>
+      <c r="L793" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M793" s="2" t="inlineStr"/>
+      <c r="N793" s="2" t="inlineStr">
+        <is>
+          <t>info@domwina.pl</t>
+        </is>
+      </c>
+      <c r="O793" s="2" t="inlineStr">
+        <is>
+          <t>+48 12 638 13 80</t>
+        </is>
+      </c>
+      <c r="P793" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q793" s="2" t="inlineStr">
+        <is>
+          <t>6771697284</t>
+        </is>
+      </c>
+      <c r="R793" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dom-wina-sp.-z-o.o./</t>
+        </is>
+      </c>
+      <c r="S793" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KlubDomuWina/</t>
+        </is>
+      </c>
+      <c r="T793" s="2" t="inlineStr"/>
+      <c r="U793" s="2" t="inlineStr"/>
+      <c r="V793" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/DworSierakowPl</t>
+        </is>
+      </c>
+      <c r="W793" s="2" t="inlineStr">
+        <is>
+          <t>Michał Stępień</t>
+        </is>
+      </c>
+      <c r="X793" s="2" t="inlineStr">
+        <is>
+          <t>Sommelier</t>
+        </is>
+      </c>
+      <c r="Y793" s="2" t="inlineStr"/>
+      <c r="Z793" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA793" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/micha%C5%82-st%C4%99pie%C5%84-2058b95b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="2" t="inlineStr">
+        <is>
+          <t>Dom Wina Sp. Z O.o.</t>
+        </is>
+      </c>
+      <c r="B794" s="2" t="inlineStr">
+        <is>
+          <t>Dom Wina Sp. Z O.o.</t>
+        </is>
+      </c>
+      <c r="C794" s="2" t="inlineStr">
+        <is>
+          <t>11076</t>
+        </is>
+      </c>
+      <c r="D794" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E794" s="2" t="inlineStr">
+        <is>
+          <t>Kraków</t>
+        </is>
+      </c>
+      <c r="F794" s="2" t="inlineStr">
+        <is>
+          <t>Małopolskie</t>
+        </is>
+      </c>
+      <c r="G794" s="2" t="inlineStr">
+        <is>
+          <t>255 Balicka</t>
+        </is>
+      </c>
+      <c r="H794" s="2" t="inlineStr">
+        <is>
+          <t>30-198</t>
+        </is>
+      </c>
+      <c r="I794" s="2" t="inlineStr">
+        <is>
+          <t>https://domwina.pl</t>
+        </is>
+      </c>
+      <c r="J794" s="2" t="inlineStr"/>
+      <c r="K794" s="2" t="inlineStr"/>
+      <c r="L794" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M794" s="2" t="inlineStr"/>
+      <c r="N794" s="2" t="inlineStr">
+        <is>
+          <t>info@domwina.pl</t>
+        </is>
+      </c>
+      <c r="O794" s="2" t="inlineStr">
+        <is>
+          <t>+48 12 638 13 80</t>
+        </is>
+      </c>
+      <c r="P794" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q794" s="2" t="inlineStr">
+        <is>
+          <t>6771697284</t>
+        </is>
+      </c>
+      <c r="R794" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dom-wina-sp.-z-o.o./</t>
+        </is>
+      </c>
+      <c r="S794" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KlubDomuWina/</t>
+        </is>
+      </c>
+      <c r="T794" s="2" t="inlineStr"/>
+      <c r="U794" s="2" t="inlineStr"/>
+      <c r="V794" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/DworSierakowPl</t>
+        </is>
+      </c>
+      <c r="W794" s="2" t="inlineStr">
+        <is>
+          <t>Katarzyna Kiełb</t>
+        </is>
+      </c>
+      <c r="X794" s="2" t="inlineStr">
+        <is>
+          <t>Assistant To The Vice President Of The Board</t>
+        </is>
+      </c>
+      <c r="Y794" s="2" t="inlineStr"/>
+      <c r="Z794" s="2" t="inlineStr"/>
+      <c r="AA794" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/katarzyna-kie%c5%82b-a443648/</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="2" t="inlineStr">
+        <is>
+          <t>Dom Wina Sp. Z O.o.</t>
+        </is>
+      </c>
+      <c r="B795" s="2" t="inlineStr">
+        <is>
+          <t>Dom Wina Sp. Z O.o.</t>
+        </is>
+      </c>
+      <c r="C795" s="2" t="inlineStr">
+        <is>
+          <t>11076</t>
+        </is>
+      </c>
+      <c r="D795" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E795" s="2" t="inlineStr">
+        <is>
+          <t>Kraków</t>
+        </is>
+      </c>
+      <c r="F795" s="2" t="inlineStr">
+        <is>
+          <t>Małopolskie</t>
+        </is>
+      </c>
+      <c r="G795" s="2" t="inlineStr">
+        <is>
+          <t>255 Balicka</t>
+        </is>
+      </c>
+      <c r="H795" s="2" t="inlineStr">
+        <is>
+          <t>30-198</t>
+        </is>
+      </c>
+      <c r="I795" s="2" t="inlineStr">
+        <is>
+          <t>https://domwina.pl</t>
+        </is>
+      </c>
+      <c r="J795" s="2" t="inlineStr"/>
+      <c r="K795" s="2" t="inlineStr"/>
+      <c r="L795" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M795" s="2" t="inlineStr"/>
+      <c r="N795" s="2" t="inlineStr">
+        <is>
+          <t>info@domwina.pl</t>
+        </is>
+      </c>
+      <c r="O795" s="2" t="inlineStr">
+        <is>
+          <t>+48 12 638 13 80</t>
+        </is>
+      </c>
+      <c r="P795" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q795" s="2" t="inlineStr">
+        <is>
+          <t>6771697284</t>
+        </is>
+      </c>
+      <c r="R795" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dom-wina-sp.-z-o.o./</t>
+        </is>
+      </c>
+      <c r="S795" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KlubDomuWina/</t>
+        </is>
+      </c>
+      <c r="T795" s="2" t="inlineStr"/>
+      <c r="U795" s="2" t="inlineStr"/>
+      <c r="V795" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/DworSierakowPl</t>
+        </is>
+      </c>
+      <c r="W795" s="2" t="inlineStr">
+        <is>
+          <t>Kacper Witek</t>
+        </is>
+      </c>
+      <c r="X795" s="2" t="inlineStr">
+        <is>
+          <t>Key Account Manager</t>
+        </is>
+      </c>
+      <c r="Y795" s="2" t="inlineStr"/>
+      <c r="Z795" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA795" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/kacper-witek-132228315/</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="2" t="inlineStr">
+        <is>
+          <t>Dom Wina Sp. Z O.o.</t>
+        </is>
+      </c>
+      <c r="B796" s="2" t="inlineStr">
+        <is>
+          <t>Dom Wina Sp. Z O.o.</t>
+        </is>
+      </c>
+      <c r="C796" s="2" t="inlineStr">
+        <is>
+          <t>11076</t>
+        </is>
+      </c>
+      <c r="D796" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E796" s="2" t="inlineStr">
+        <is>
+          <t>Kraków</t>
+        </is>
+      </c>
+      <c r="F796" s="2" t="inlineStr">
+        <is>
+          <t>Małopolskie</t>
+        </is>
+      </c>
+      <c r="G796" s="2" t="inlineStr">
+        <is>
+          <t>255 Balicka</t>
+        </is>
+      </c>
+      <c r="H796" s="2" t="inlineStr">
+        <is>
+          <t>30-198</t>
+        </is>
+      </c>
+      <c r="I796" s="2" t="inlineStr">
+        <is>
+          <t>https://domwina.pl</t>
+        </is>
+      </c>
+      <c r="J796" s="2" t="inlineStr"/>
+      <c r="K796" s="2" t="inlineStr"/>
+      <c r="L796" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M796" s="2" t="inlineStr"/>
+      <c r="N796" s="2" t="inlineStr">
+        <is>
+          <t>info@domwina.pl</t>
+        </is>
+      </c>
+      <c r="O796" s="2" t="inlineStr">
+        <is>
+          <t>+48 12 638 13 80</t>
+        </is>
+      </c>
+      <c r="P796" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q796" s="2" t="inlineStr">
+        <is>
+          <t>6771697284</t>
+        </is>
+      </c>
+      <c r="R796" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dom-wina-sp.-z-o.o./</t>
+        </is>
+      </c>
+      <c r="S796" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KlubDomuWina/</t>
+        </is>
+      </c>
+      <c r="T796" s="2" t="inlineStr"/>
+      <c r="U796" s="2" t="inlineStr"/>
+      <c r="V796" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/DworSierakowPl</t>
+        </is>
+      </c>
+      <c r="W796" s="2" t="inlineStr">
+        <is>
+          <t>Artur Boruta</t>
+        </is>
+      </c>
+      <c r="X796" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y796" s="2" t="inlineStr"/>
+      <c r="Z796" s="2" t="inlineStr"/>
+      <c r="AA796" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/artur-boruta-1a643a13/</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="2" t="inlineStr">
+        <is>
+          <t>Dom Wina Sp. Z O.o.</t>
+        </is>
+      </c>
+      <c r="B797" s="2" t="inlineStr">
+        <is>
+          <t>Dom Wina Sp. Z O.o.</t>
+        </is>
+      </c>
+      <c r="C797" s="2" t="inlineStr">
+        <is>
+          <t>11076</t>
+        </is>
+      </c>
+      <c r="D797" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E797" s="2" t="inlineStr">
+        <is>
+          <t>Kraków</t>
+        </is>
+      </c>
+      <c r="F797" s="2" t="inlineStr">
+        <is>
+          <t>Małopolskie</t>
+        </is>
+      </c>
+      <c r="G797" s="2" t="inlineStr">
+        <is>
+          <t>255 Balicka</t>
+        </is>
+      </c>
+      <c r="H797" s="2" t="inlineStr">
+        <is>
+          <t>30-198</t>
+        </is>
+      </c>
+      <c r="I797" s="2" t="inlineStr">
+        <is>
+          <t>https://domwina.pl</t>
+        </is>
+      </c>
+      <c r="J797" s="2" t="inlineStr"/>
+      <c r="K797" s="2" t="inlineStr"/>
+      <c r="L797" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M797" s="2" t="inlineStr"/>
+      <c r="N797" s="2" t="inlineStr">
+        <is>
+          <t>info@domwina.pl</t>
+        </is>
+      </c>
+      <c r="O797" s="2" t="inlineStr">
+        <is>
+          <t>+48 12 638 13 80</t>
+        </is>
+      </c>
+      <c r="P797" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q797" s="2" t="inlineStr">
+        <is>
+          <t>6771697284</t>
+        </is>
+      </c>
+      <c r="R797" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dom-wina-sp.-z-o.o./</t>
+        </is>
+      </c>
+      <c r="S797" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KlubDomuWina/</t>
+        </is>
+      </c>
+      <c r="T797" s="2" t="inlineStr"/>
+      <c r="U797" s="2" t="inlineStr"/>
+      <c r="V797" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/DworSierakowPl</t>
+        </is>
+      </c>
+      <c r="W797" s="2" t="inlineStr">
+        <is>
+          <t>Lech Andrzejewski</t>
+        </is>
+      </c>
+      <c r="X797" s="2" t="inlineStr">
+        <is>
+          <t>Sales Representative, Wine Advisor</t>
+        </is>
+      </c>
+      <c r="Y797" s="2" t="inlineStr"/>
+      <c r="Z797" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA797" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/lech-andrzejewski/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Poland.xlsx
+++ b/BWI/bestwine_output/bestwine_Poland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA797"/>
+  <dimension ref="A1:AA801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -84216,6 +84216,370 @@
         </is>
       </c>
     </row>
+    <row r="798">
+      <c r="A798" s="2" t="inlineStr">
+        <is>
+          <t>P H U Carmen Lukasz Kubiak</t>
+        </is>
+      </c>
+      <c r="B798" s="2" t="inlineStr">
+        <is>
+          <t>P H U Carmen Lukasz Kubiak</t>
+        </is>
+      </c>
+      <c r="C798" s="2" t="inlineStr">
+        <is>
+          <t>55284</t>
+        </is>
+      </c>
+      <c r="D798" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E798" s="2" t="inlineStr">
+        <is>
+          <t>Słodków-Kolonia</t>
+        </is>
+      </c>
+      <c r="F798" s="2" t="inlineStr">
+        <is>
+          <t>Wielkopolskie, Powiat turecki</t>
+        </is>
+      </c>
+      <c r="G798" s="2" t="inlineStr">
+        <is>
+          <t>Słodków Kolonia 56h</t>
+        </is>
+      </c>
+      <c r="H798" s="2" t="inlineStr">
+        <is>
+          <t>62-700</t>
+        </is>
+      </c>
+      <c r="I798" s="2" t="inlineStr">
+        <is>
+          <t>https://carmen.turek.pl</t>
+        </is>
+      </c>
+      <c r="J798" s="2" t="inlineStr"/>
+      <c r="K798" s="2" t="inlineStr"/>
+      <c r="L798" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="M798" s="2" t="inlineStr"/>
+      <c r="N798" s="2" t="inlineStr">
+        <is>
+          <t>sklepcarmen-zeromskiego@wp.pl</t>
+        </is>
+      </c>
+      <c r="O798" s="2" t="inlineStr">
+        <is>
+          <t>+48 63 278 38 72</t>
+        </is>
+      </c>
+      <c r="P798" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q798" s="2" t="inlineStr">
+        <is>
+          <t>6681729419</t>
+        </is>
+      </c>
+      <c r="R798" s="2" t="inlineStr"/>
+      <c r="S798" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/P.H.U.Carmen/</t>
+        </is>
+      </c>
+      <c r="T798" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sklepymonopolowecarmen/</t>
+        </is>
+      </c>
+      <c r="U798" s="2" t="inlineStr"/>
+      <c r="V798" s="2" t="inlineStr"/>
+      <c r="W798" s="2" t="inlineStr"/>
+      <c r="X798" s="2" t="inlineStr"/>
+      <c r="Y798" s="2" t="inlineStr"/>
+      <c r="Z798" s="2" t="inlineStr"/>
+      <c r="AA798" s="2" t="inlineStr"/>
+    </row>
+    <row r="799">
+      <c r="A799" s="2" t="inlineStr">
+        <is>
+          <t>Ars Vini Sp Zo.o. Sp.k</t>
+        </is>
+      </c>
+      <c r="B799" s="2" t="inlineStr">
+        <is>
+          <t>Ars Vini Sp Zo.o. Sp.k</t>
+        </is>
+      </c>
+      <c r="C799" s="2" t="inlineStr">
+        <is>
+          <t>46794</t>
+        </is>
+      </c>
+      <c r="D799" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E799" s="2" t="inlineStr">
+        <is>
+          <t>Wrocław</t>
+        </is>
+      </c>
+      <c r="F799" s="2" t="inlineStr">
+        <is>
+          <t>Dolnośląskie</t>
+        </is>
+      </c>
+      <c r="G799" s="2" t="inlineStr">
+        <is>
+          <t>45/3 Zwycięska</t>
+        </is>
+      </c>
+      <c r="H799" s="2" t="inlineStr">
+        <is>
+          <t>53-033</t>
+        </is>
+      </c>
+      <c r="I799" s="2" t="inlineStr">
+        <is>
+          <t>https://arsvini.pl</t>
+        </is>
+      </c>
+      <c r="J799" s="2" t="inlineStr"/>
+      <c r="K799" s="2" t="inlineStr"/>
+      <c r="L799" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M799" s="2" t="inlineStr"/>
+      <c r="N799" s="2" t="inlineStr">
+        <is>
+          <t>arsvini@arsvini.pl</t>
+        </is>
+      </c>
+      <c r="O799" s="2" t="inlineStr"/>
+      <c r="P799" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q799" s="2" t="inlineStr">
+        <is>
+          <t>8961538495</t>
+        </is>
+      </c>
+      <c r="R799" s="2" t="inlineStr"/>
+      <c r="S799" s="2" t="inlineStr"/>
+      <c r="T799" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ars.vini</t>
+        </is>
+      </c>
+      <c r="U799" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/ARSVINIpl</t>
+        </is>
+      </c>
+      <c r="V799" s="2" t="inlineStr"/>
+      <c r="W799" s="2" t="inlineStr">
+        <is>
+          <t>Aleksandra Jez</t>
+        </is>
+      </c>
+      <c r="X799" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="Y799" s="2" t="inlineStr"/>
+      <c r="Z799" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA799" s="2" t="inlineStr"/>
+    </row>
+    <row r="800">
+      <c r="A800" s="2" t="inlineStr">
+        <is>
+          <t>Ars Vini Sp Zo.o. Sp.k</t>
+        </is>
+      </c>
+      <c r="B800" s="2" t="inlineStr">
+        <is>
+          <t>Ars Vini Sp Zo.o. Sp.k</t>
+        </is>
+      </c>
+      <c r="C800" s="2" t="inlineStr">
+        <is>
+          <t>46794</t>
+        </is>
+      </c>
+      <c r="D800" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E800" s="2" t="inlineStr">
+        <is>
+          <t>Wrocław</t>
+        </is>
+      </c>
+      <c r="F800" s="2" t="inlineStr">
+        <is>
+          <t>Dolnośląskie</t>
+        </is>
+      </c>
+      <c r="G800" s="2" t="inlineStr">
+        <is>
+          <t>45/3 Zwycięska</t>
+        </is>
+      </c>
+      <c r="H800" s="2" t="inlineStr">
+        <is>
+          <t>53-033</t>
+        </is>
+      </c>
+      <c r="I800" s="2" t="inlineStr">
+        <is>
+          <t>https://arsvini.pl</t>
+        </is>
+      </c>
+      <c r="J800" s="2" t="inlineStr"/>
+      <c r="K800" s="2" t="inlineStr"/>
+      <c r="L800" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M800" s="2" t="inlineStr"/>
+      <c r="N800" s="2" t="inlineStr">
+        <is>
+          <t>arsvini@arsvini.pl</t>
+        </is>
+      </c>
+      <c r="O800" s="2" t="inlineStr"/>
+      <c r="P800" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q800" s="2" t="inlineStr">
+        <is>
+          <t>8961538495</t>
+        </is>
+      </c>
+      <c r="R800" s="2" t="inlineStr"/>
+      <c r="S800" s="2" t="inlineStr"/>
+      <c r="T800" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ars.vini</t>
+        </is>
+      </c>
+      <c r="U800" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/ARSVINIpl</t>
+        </is>
+      </c>
+      <c r="V800" s="2" t="inlineStr"/>
+      <c r="W800" s="2" t="inlineStr">
+        <is>
+          <t>Lidia Andrzejewska</t>
+        </is>
+      </c>
+      <c r="X800" s="2" t="inlineStr">
+        <is>
+          <t>Wine Buyer</t>
+        </is>
+      </c>
+      <c r="Y800" s="2" t="inlineStr"/>
+      <c r="Z800" s="2" t="inlineStr"/>
+      <c r="AA800" s="2" t="inlineStr"/>
+    </row>
+    <row r="801">
+      <c r="A801" s="2" t="inlineStr">
+        <is>
+          <t>Viñola Hiszpańskie Wina</t>
+        </is>
+      </c>
+      <c r="B801" s="2" t="inlineStr">
+        <is>
+          <t>Viñola Hiszpańskie Wina</t>
+        </is>
+      </c>
+      <c r="C801" s="2" t="inlineStr">
+        <is>
+          <t>11308</t>
+        </is>
+      </c>
+      <c r="D801" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E801" s="2" t="inlineStr">
+        <is>
+          <t>Poznań</t>
+        </is>
+      </c>
+      <c r="F801" s="2" t="inlineStr"/>
+      <c r="G801" s="2" t="inlineStr">
+        <is>
+          <t>Kościelna 19</t>
+        </is>
+      </c>
+      <c r="H801" s="2" t="inlineStr">
+        <is>
+          <t>60-536</t>
+        </is>
+      </c>
+      <c r="I801" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinola.pl</t>
+        </is>
+      </c>
+      <c r="J801" s="2" t="inlineStr"/>
+      <c r="K801" s="2" t="inlineStr"/>
+      <c r="L801" s="2" t="inlineStr"/>
+      <c r="M801" s="2" t="inlineStr"/>
+      <c r="N801" s="2" t="inlineStr">
+        <is>
+          <t>sklepellocal@gmail.com</t>
+        </is>
+      </c>
+      <c r="O801" s="2" t="inlineStr"/>
+      <c r="P801" s="2" t="inlineStr"/>
+      <c r="Q801" s="2" t="inlineStr"/>
+      <c r="R801" s="2" t="inlineStr"/>
+      <c r="S801" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/localsklephiszpanski</t>
+        </is>
+      </c>
+      <c r="T801" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sklepellocal/</t>
+        </is>
+      </c>
+      <c r="U801" s="2" t="inlineStr"/>
+      <c r="V801" s="2" t="inlineStr"/>
+      <c r="W801" s="2" t="inlineStr"/>
+      <c r="X801" s="2" t="inlineStr"/>
+      <c r="Y801" s="2" t="inlineStr"/>
+      <c r="Z801" s="2" t="inlineStr"/>
+      <c r="AA801" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
